--- a/data/fpl_master_projections.xlsx
+++ b/data/fpl_master_projections.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Raya is projected for 5.08 pts in GW7 and 21.4 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); High clean sheet odds for upcoming fixture (47.3%)</t>
+          <t>Raya is projected for 5.08 pts in GW8 and 21.4 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); High clean sheet odds for upcoming fixture (47.3%)</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Arrizabalaga offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Arrizabalaga offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Meslier offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Meslier offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Gabriel offers stable output (4.07 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gabriel offers stable output (4.07 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>J.Timber carries elevated risk for GW7 (0.42 exp pts). Concerns: Rotation risk (only 12% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>J.Timber carries elevated risk for GW8 (0.42 exp pts). Concerns: Rotation risk (only 12% projected start); Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Saliba offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Saliba carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Back injury - Unknown return date; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Lewis-Skelly offers stable output (1.92 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lewis-Skelly offers stable output (1.92 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Calafiori is projected for 4.92 pts in GW7 and 20.6 pts over next 5 weeks. Key drivers: Nailed starter (93% expected start probability); High clean sheet odds for upcoming fixture (47.3%); Attacking defender upside (0.19 xG/90, 0.15 xA/90)</t>
+          <t>Calafiori is projected for 4.92 pts in GW8 and 20.6 pts over next 5 weeks. Key drivers: Nailed starter (93% expected start probability); High clean sheet odds for upcoming fixture (47.3%); Attacking defender upside (0.19 xG/90, 0.15 xA/90)</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Hincapie offers stable output (0.01 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hincapie carries elevated risk for GW8 (0.01 exp pts). Concerns: Injury doubt: Ankle injury - 75% chance of playing; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>White carries elevated risk for GW7 (2.93 exp pts). Concerns: Rotation risk (only 59% projected start); Regression warning: projected PPG is -2.80 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>White carries elevated risk for GW8 (2.93 exp pts). Concerns: Rotation risk (only 59% projected start); Regression warning: projected PPG is -2.80 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Mosquera carries elevated risk for GW7 (0.68 exp pts). Concerns: Rotation risk (only 13% projected start); Regression warning: projected PPG is -5.52 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Mosquera carries elevated risk for GW8 (0.68 exp pts). Concerns: Rotation risk (only 13% projected start); Regression warning: projected PPG is -5.52 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Doubtful (Monitor)</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Saka is projected for 3.95 pts in GW7 and 22.2 pts over next 5 weeks. Key drivers: Strong goal threat (36.5% anytime goal odds); High-frequency chance generator (0.55 xG per 90); Designated penalty taker</t>
+          <t>Saka carries an injury flag (Thigh injury - 50% chance of playing). Projected for 3.95 pts in GW8 (minutes discounted to 47%) and 22.2 pts over next 5 weeks.</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Rice offers stable output (3.82 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Rice offers stable output (3.82 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Eze carries elevated risk for GW7 (1.10 exp pts). Concerns: Rotation risk (only 10% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Eze carries elevated risk for GW8 (1.10 exp pts). Concerns: Rotation risk (only 10% projected start); Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Ødegaard is projected for 4.36 pts in GW7 and 20.4 pts over next 5 weeks. Key drivers: Primary creative playmaker (0.26 xA per 90)</t>
+          <t>Ødegaard is projected for 4.36 pts in GW8 and 20.4 pts over next 5 weeks. Key drivers: Primary creative playmaker (0.26 xA per 90)</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Madueke carries elevated risk for GW7 (1.07 exp pts). Concerns: Rotation risk (only 12% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Madueke carries elevated risk for GW8 (1.07 exp pts). Concerns: Rotation risk (only 12% projected start); Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Merino offers stable output (0.32 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Merino offers stable output (0.32 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>Martinelli carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Martinelli carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Al Hilal permanently; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Zubimendi offers stable output (0.27 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Zubimendi offers stable output (0.27 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Dowman offers stable output (0.72 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dowman offers stable output (0.72 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Nwaneri offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Nwaneri carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Borussia Dortmund on loan for the rest of the season; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>Fábio Vieira offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Fábio Vieira carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Hamburger SV permanently; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Nelson offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Nelson carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: has departed the club as a free agent.; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Gyökeres carries elevated risk for GW7 (0.26 exp pts). Concerns: Rotation risk (only 6% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Gyökeres carries elevated risk for GW8 (0.26 exp pts). Concerns: Rotation risk (only 6% projected start); Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Havertz offers stable output (3.73 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Havertz offers stable output (3.73 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>G.Jesus offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>G.Jesus carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined FC Barcelona permanently; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Konsa carries elevated risk for GW7 (2.88 exp pts). Concerns: Rotation risk (only 62% projected start); Regression warning: projected PPG is -1.61 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Konsa carries elevated risk for GW8 (2.88 exp pts). Concerns: Rotation risk (only 62% projected start); Regression warning: projected PPG is -1.61 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Bruno G. carries elevated risk for GW7 (0.77 exp pts). Concerns: Rotation risk (only 17% projected start); Regression warning: projected PPG is -3.45 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Bruno G. carries elevated risk for GW8 (0.77 exp pts). Concerns: Rotation risk (only 17% projected start); Regression warning: projected PPG is -3.45 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Tzolis carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Tzolis carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Expected back 1 Nov; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>M.Bizot offers stable output (0.29 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>M.Bizot offers stable output (0.29 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>Digne offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Digne carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Paris Saint-Germain permanently; Low defensive odds; clean sheet unlikely (16.9%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>Cash offers stable output (1.87 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Cash offers stable output (1.87 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>Mings offers stable output (1.98 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mings offers stable output (1.98 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>Pau offers stable output (0.68 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Pau offers stable output (0.68 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Bogarde offers stable output (0.14 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bogarde offers stable output (0.14 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Maatsen offers stable output (1.70 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Maatsen offers stable output (1.70 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>Lindelöf offers stable output (2.20 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lindelöf offers stable output (2.20 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>A.García offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>A.García carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Getafe on loan for the rest of the season; Low defensive odds; clean sheet unlikely (16.9%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Nedeljkovic offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Nedeljkovic carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Rangers on loan for the rest of the season; Low defensive odds; clean sheet unlikely (16.9%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>Buendía offers stable output (3.32 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Buendía offers stable output (3.32 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>Bailey offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bailey carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Olympiakos permanently; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>McGinn offers stable output (3.14 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>McGinn offers stable output (3.14 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>Barkley offers stable output (1.95 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Barkley offers stable output (1.95 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>Kamara offers stable output (2.65 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kamara offers stable output (2.65 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>Onana offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Onana carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>Iling Jr offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Iling Jr carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Bolton Wanderers on loan for the rest of the season; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>Burrowes offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Burrowes offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>George Hemmings offers stable output (1.10 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>George Hemmings offers stable output (1.10 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>Alysson offers stable output (0.21 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Alysson offers stable output (0.21 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>Manzambi carries elevated risk for GW7 (1.42 exp pts). Concerns: Rotation risk (only 15% projected start); Regression warning: projected PPG is -6.32 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Manzambi carries elevated risk for GW8 (1.42 exp pts). Concerns: Injury doubt: Calf injury - 75% chance of playing; Regression warning: projected PPG is -6.32 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>Gomes offers stable output (0.60 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gomes offers stable output (0.60 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>Watkins carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 0.9)</t>
+          <t>Watkins carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Al Hilal permanently; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>Abraham offers stable output (0.79 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Abraham offers stable output (0.79 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>Garnacho offers stable output (0.02 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Garnacho offers stable output (0.02 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>N.Jackson offers stable output (3.05 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>N.Jackson offers stable output (3.05 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>Madjo offers stable output (0.59 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Madjo offers stable output (0.59 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Ruggeri offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ruggeri carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Expected back 2 Jan; Low defensive odds; clean sheet unlikely (16.9%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>Suzuki offers stable output (2.96 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Suzuki offers stable output (2.96 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>Rowe offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Rowe offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>Lynch offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lynch carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Oxford United on loan until January; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>Wan-Bissaka offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Wan-Bissaka carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Expected back 21 Nov; Low defensive odds; clean sheet unlikely (16.9%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>Goretzka offers stable output (0.28 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Goretzka offers stable output (0.28 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>Harwood-Bellis offers stable output (0.22 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Harwood-Bellis offers stable output (0.22 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>Mbaye carries elevated risk for GW7 (0.69 exp pts). Concerns: Rotation risk (only 6% projected start); Tough offensive matchup (FDR: 0.9)</t>
+          <t>Mbaye carries elevated risk for GW8 (0.69 exp pts). Concerns: Rotation risk (only 6% projected start); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>Wright offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Wright offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>Petrović offers stable output (2.70 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Petrović offers stable output (2.70 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>Forster offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Forster offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>Dennis offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dennis carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined MK Dons permanently; Low defensive odds; clean sheet unlikely (20.3%); Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>Hill offers stable output (2.42 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hill offers stable output (2.42 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>Truffert offers stable output (2.45 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Truffert offers stable output (2.45 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>Diakité offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Diakité offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>Milosavljević offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Milosavljević carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Thigh injury - Expected back 8 Nov; Low defensive odds; clean sheet unlikely (20.3%); Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>Smith offers stable output (2.12 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Smith offers stable output (2.12 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>J.Araujo offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>J.Araujo carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Thigh injury - Unknown return date; Low defensive odds; clean sheet unlikely (20.3%); Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>Soler offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Soler offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>Rayan offers stable output (3.17 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Rayan offers stable output (3.17 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>Tavernier is projected for 4.45 pts in GW7 and 23.4 pts over next 5 weeks. Key drivers: Nailed starter (91% expected start probability); Strong goal threat (29.7% anytime goal odds); High-frequency chance generator (0.45 xG per 90)</t>
+          <t>Tavernier is projected for 4.45 pts in GW8 and 23.4 pts over next 5 weeks. Key drivers: Nailed starter (91% expected start probability); Strong goal threat (29.7% anytime goal odds); High-frequency chance generator (0.45 xG per 90)</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>Scott carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -4.34 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Scott carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Thigh injury - Expected back 8 Nov; Regression warning: projected PPG is -4.34 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>Kluivert offers stable output (2.17 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kluivert offers stable output (2.17 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>Cook offers stable output (0.79 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Cook offers stable output (0.79 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>Gannon-Doak offers stable output (0.59 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gannon-Doak offers stable output (0.59 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>Adams offers stable output (2.27 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Adams offers stable output (2.27 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>Brooks offers stable output (0.69 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Brooks offers stable output (0.69 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>Christie offers stable output (1.17 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Christie offers stable output (1.17 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>Tóth.A offers stable output (0.01 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tóth.A offers stable output (0.01 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>Adli offers stable output (0.49 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Adli offers stable output (0.49 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>Kroupi.Jr carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Kroupi.Jr carries elevated risk for GW8 (0.00 exp pts). Concerns: Injury doubt: Foot injury - 50% chance of playing; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>Evanilson carries elevated risk for GW7 (3.72 exp pts). Concerns: Regression warning: projected PPG is -1.42 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Evanilson carries elevated risk for GW8 (3.72 exp pts). Concerns: Regression warning: projected PPG is -1.42 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>Enes Ünal offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Enes Ünal carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Getafe permanently; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>Rodríguez carries elevated risk for GW7 (0.03 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Rodríguez carries elevated risk for GW8 (0.03 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>Silva offers stable output (2.48 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Silva offers stable output (2.48 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>Sanchez offers stable output (0.01 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Sanchez offers stable output (0.01 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>Jebbison offers stable output (0.02 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Jebbison offers stable output (0.02 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>Di Gregorio offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Di Gregorio offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>Kelleher offers stable output (4.11 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kelleher offers stable output (4.11 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>Valdimarsson offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Valdimarsson offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>Collins offers stable output (0.78 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Collins offers stable output (0.78 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>Van den Berg offers stable output (0.26 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Van den Berg offers stable output (0.26 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>Lewis-Potter offers stable output (3.97 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lewis-Potter offers stable output (3.97 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9560,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>Ajer carries elevated risk for GW7 (3.19 exp pts). Concerns: Regression warning: projected PPG is -1.42 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Ajer carries elevated risk for GW8 (3.19 exp pts). Concerns: Regression warning: projected PPG is -1.42 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>Kayode offers stable output (2.77 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kayode offers stable output (2.77 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>Henry offers stable output (0.23 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Henry offers stable output (0.23 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>Hickey offers stable output (0.78 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hickey offers stable output (0.78 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>Ji-soo offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ji-soo offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>Schuster carries elevated risk for GW7 (0.96 exp pts). Concerns: Rotation risk (only 17% projected start); Regression warning: projected PPG is -4.62 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Schuster carries elevated risk for GW8 (0.96 exp pts). Concerns: Injury doubt: Ankle injury - 75% chance of playing; Regression warning: projected PPG is -4.62 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>Schade is projected for 4.36 pts in GW7 and 19.7 pts over next 5 weeks. Key drivers: Strong goal threat (35.5% anytime goal odds)</t>
+          <t>Schade is projected for 4.36 pts in GW8 and 19.7 pts over next 5 weeks. Key drivers: Strong goal threat (35.5% anytime goal odds)</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>O.Dango carries elevated risk for GW7 (1.41 exp pts). Concerns: Rotation risk (only 19% projected start); Tough offensive matchup (FDR: 1.4)</t>
+          <t>O.Dango carries elevated risk for GW8 (1.41 exp pts). Concerns: Rotation risk (only 19% projected start); Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>Damsgaard offers stable output (1.48 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Damsgaard offers stable output (1.48 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>Jensen offers stable output (0.80 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Jensen offers stable output (0.80 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>Janelt carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -2.68 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Janelt carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Suspended until 31 Oct; Regression warning: projected PPG is -2.68 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>Milambo offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Milambo carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>Carvalho carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -6.00 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Carvalho carries elevated risk for GW8 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -6.00 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>Yarmoliuk offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Yarmoliuk carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Suspended until 8 Nov; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>Dasilva offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dasilva carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Unknown return date; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>Anthony offers stable output (3.13 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Anthony offers stable output (3.13 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>Thiago offers stable output (3.55 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Thiago offers stable output (3.55 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>Furo offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Furo carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Unspecified injury - Unknown return date; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>Wilson offers stable output (0.83 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Wilson offers stable output (0.83 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>M.Sangaré offers stable output (2.04 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>M.Sangaré offers stable output (2.04 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>Diouf offers stable output (0.66 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Diouf offers stable output (0.66 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>Nunes offers stable output (0.61 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Nunes offers stable output (0.61 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>Fredrick offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Fredrick offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11630,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>Balcombe offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Balcombe offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>Verbruggen carries elevated risk for GW7 (3.08 exp pts). Concerns: Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -1.75 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Verbruggen carries elevated risk for GW8 (3.08 exp pts). Concerns: Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -1.75 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>Steele offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Steele offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>F.Kadıoğlu carries elevated risk for GW7 (2.16 exp pts). Concerns: Rotation risk (only 69% projected start); Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -2.26 lower than past form</t>
+          <t>F.Kadıoğlu carries elevated risk for GW8 (2.16 exp pts). Concerns: Rotation risk (only 69% projected start); Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -2.26 lower than past form</t>
         </is>
       </c>
     </row>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>Boscagli carries elevated risk for GW7 (2.35 exp pts). Concerns: Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -2.21 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Boscagli carries elevated risk for GW8 (2.35 exp pts). Concerns: Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -2.21 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -12080,7 +12080,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>De Cuyper is projected for 3.74 pts in GW7 and 21.2 pts over next 5 weeks. Key drivers: Nailed starter (92% expected start probability); Attacking defender upside (0.28 xG/90, 0.12 xA/90)</t>
+          <t>De Cuyper is projected for 3.74 pts in GW8 and 21.2 pts over next 5 weeks. Key drivers: Nailed starter (92% expected start probability); Attacking defender upside (0.28 xG/90, 0.12 xA/90)</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>Dunk carries elevated risk for GW7 (2.22 exp pts). Concerns: Rotation risk (only 64% projected start); Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -2.52 lower than past form</t>
+          <t>Dunk carries elevated risk for GW8 (2.22 exp pts). Concerns: Rotation risk (only 64% projected start); Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -2.52 lower than past form</t>
         </is>
       </c>
     </row>
@@ -12260,7 +12260,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>Coppola offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Coppola offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -12288,7 +12288,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>Igor offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Igor carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Burnley permanently; Low defensive odds; clean sheet unlikely (20.5%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>Costinha offers stable output (0.23 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Costinha offers stable output (0.23 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>Svoboda offers stable output (0.21 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Svoboda offers stable output (0.21 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -12558,7 +12558,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>Mitoma offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mitoma carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Expected back 31 Oct; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>Minteh offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Minteh carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Leg injury - Expected back 28 Nov; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>Hinshelwood carries elevated risk for GW7 (0.89 exp pts). Concerns: Rotation risk (only 6% projected start); Regression warning: projected PPG is -10.49 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Hinshelwood carries elevated risk for GW8 (0.89 exp pts). Concerns: Rotation risk (only 6% projected start); Regression warning: projected PPG is -10.49 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>Groß is projected for 4.02 pts in GW7 and 21.1 pts over next 5 weeks. Key drivers: Nailed starter (96% expected start probability); Designated penalty taker</t>
+          <t>Groß is projected for 4.02 pts in GW8 and 21.1 pts over next 5 weeks. Key drivers: Nailed starter (96% expected start probability); Designated penalty taker</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>Georginio offers stable output (1.01 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Georginio offers stable output (1.01 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>O'Riley offers stable output (0.56 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>O'Riley offers stable output (0.56 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -13160,7 +13160,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>Gomez carries elevated risk for GW7 (3.46 exp pts). Concerns: Regression warning: projected PPG is -1.99 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Gomez carries elevated risk for GW8 (3.46 exp pts). Concerns: Regression warning: projected PPG is -1.99 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>Buonanotte offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Buonanotte carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Elche on loan for the rest of the season; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -13340,7 +13340,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>Ayari carries elevated risk for GW7 (3.06 exp pts). Concerns: Rotation risk (only 67% projected start); Regression warning: projected PPG is -2.31 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Ayari carries elevated risk for GW8 (3.06 exp pts). Concerns: Rotation risk (only 67% projected start); Regression warning: projected PPG is -2.31 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>Wieffer offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Wieffer carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Low defensive odds; clean sheet unlikely (20.5%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>Howell offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Howell carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Leicester City on loan for the rest of the season; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>Watson offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Watson carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Leicester City on loan for the rest of the season; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -13700,7 +13700,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>Oriola offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Oriola offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>Yohanna offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Yohanna carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Unspecified injury - Expected back 31 Oct; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -13818,7 +13818,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>Tzimas offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tzimas carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>Kostoulas carries elevated risk for GW7 (3.43 exp pts). Concerns: Rotation risk (only 65% projected start); Regression warning: projected PPG is -2.70 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Kostoulas carries elevated risk for GW8 (3.43 exp pts). Concerns: Rotation risk (only 65% projected start); Regression warning: projected PPG is -2.70 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>Ferguson offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ferguson carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Ankle injury - Unknown return date; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -14088,7 +14088,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>Struijk offers stable output (0.34 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Struijk carries elevated risk for GW8 (0.34 exp pts). Concerns: Injury doubt: Hamstring injury - 75% chance of playing; Low defensive odds; clean sheet unlikely (20.5%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -14240,7 +14240,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>Vuskovic carries elevated risk for GW7 (2.89 exp pts). Concerns: Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -3.86 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Vuskovic carries elevated risk for GW8 (2.89 exp pts). Concerns: Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -3.86 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>David offers stable output (0.69 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>David offers stable output (0.69 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>Osman offers stable output (0.59 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Osman offers stable output (0.59 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>Yalcouyé offers stable output (0.95 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Yalcouyé offers stable output (0.95 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>Hadjam carries elevated risk for GW7 (0.27 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -3.94 lower than past form</t>
+          <t>Hadjam carries elevated risk for GW8 (0.27 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -3.94 lower than past form</t>
         </is>
       </c>
     </row>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>Cozier-Duberry offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Cozier-Duberry carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Middlesbrough on loan for the rest of the season; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>Andrés carries elevated risk for GW7 (1.02 exp pts). Concerns: Rotation risk (only 22% projected start); Regression warning: projected PPG is -3.35 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Andrés carries elevated risk for GW8 (1.02 exp pts). Concerns: Rotation risk (only 22% projected start); Regression warning: projected PPG is -3.35 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -14808,7 +14808,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -14870,7 +14870,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>Azeez offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Azeez carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Expected back 31 Oct; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>Ibrahim offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ibrahim offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -15050,7 +15050,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>Martinez offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Martinez carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Head injury - Unknown return date; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>Rogers is projected for 4.34 pts in GW7 and 19.6 pts over next 5 weeks. Key drivers: Nailed starter (96% expected start probability); Strong goal threat (36.0% anytime goal odds)</t>
+          <t>Rogers is projected for 4.34 pts in GW8 and 19.6 pts over next 5 weeks. Key drivers: Nailed starter (96% expected start probability); Strong goal threat (36.0% anytime goal odds)</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>Henderson carries elevated risk for GW7 (1.21 exp pts). Concerns: Rotation risk (only 21% projected start); Regression warning: projected PPG is -6.71 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
+          <t>Henderson carries elevated risk for GW8 (1.21 exp pts). Concerns: Rotation risk (only 21% projected start); Regression warning: projected PPG is -6.71 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -15320,7 +15320,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>Welbeck offers stable output (1.17 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Welbeck offers stable output (1.17 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -15348,7 +15348,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>Sánchez offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Sánchez carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Como on loan for the rest of the season; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>Jörgensen offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Jörgensen carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined RC Strasbourg on loan for the rest of the season; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>James offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>James carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>Chalobah offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Chalobah carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Como permanently; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>Gusto offers stable output (0.80 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gusto carries elevated risk for GW8 (0.80 exp pts). Concerns: Injury doubt: Illness - 75% chance of playing; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>Fofana offers stable output (0.95 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Fofana offers stable output (0.95 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>B.Badiashile offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>B.Badiashile carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Napoli on loan for the rest of the season; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>Hato offers stable output (1.93 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hato offers stable output (1.93 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>Colwill offers stable output (2.59 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Colwill offers stable output (2.59 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -16220,7 +16220,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>M.Sarr offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>M.Sarr carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Real Sociedad on loan for the rest of the season; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>Acheampong offers stable output (1.89 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Acheampong offers stable output (1.89 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>Palestra offers stable output (0.28 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Palestra offers stable output (0.28 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -16490,7 +16490,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>Palmer is projected for 4.22 pts in GW7 and 18.1 pts over next 5 weeks. Key drivers: Nailed starter (98% expected start probability); Elite bookmaker goal probability (41.5% anytime); Designated penalty taker</t>
+          <t>Palmer is projected for 4.22 pts in GW8 and 18.1 pts over next 5 weeks. Key drivers: Nailed starter (98% expected start probability); Elite bookmaker goal probability (41.5% anytime); Designated penalty taker</t>
         </is>
       </c>
     </row>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>Neto carries elevated risk for GW7 (3.69 exp pts). Concerns: Rotation risk (only 68% projected start); Regression warning: projected PPG is -1.63 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
+          <t>Neto carries elevated risk for GW8 (3.69 exp pts). Concerns: Rotation risk (only 68% projected start); Regression warning: projected PPG is -1.63 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>Estêvão carries elevated risk for GW7 (0.02 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.3)</t>
+          <t>Estêvão carries elevated risk for GW8 (0.02 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -16760,7 +16760,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>Gittens offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gittens carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Ankle injury - Unknown return date; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>Caicedo offers stable output (0.51 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Caicedo offers stable output (0.51 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>Lavia offers stable output (1.07 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lavia offers stable output (1.07 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>D.Essugo offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>D.Essugo carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined RC Strasbourg on loan for the rest of the season; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -17120,7 +17120,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>Quenda offers stable output (0.67 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Quenda offers stable output (0.67 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>João Pedro offers stable output (3.97 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>João Pedro offers stable output (3.97 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>Marc Guiu offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Marc Guiu carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined RB Leipzig permanently; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>Mheuka offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mheuka offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -17418,7 +17418,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>Emegha offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Emegha carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Unknown return date; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>Lacroix offers stable output (3.04 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lacroix offers stable output (3.04 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -17660,7 +17660,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>Penders offers stable output (0.02 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Penders offers stable output (0.02 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>Anselmino offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Anselmino offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>Barco offers stable output (0.64 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Barco offers stable output (0.64 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>Chavarria offers stable output (0.62 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Chavarria carries elevated risk for GW8 (0.62 exp pts). Concerns: Injury doubt: Unspecified injury - 75% chance of playing; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18020,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>Nicoll-Jazuli offers stable output (0.29 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Nicoll-Jazuli offers stable output (0.29 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -18110,7 +18110,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>Pinnock offers stable output (2.19 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Pinnock offers stable output (2.19 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>Onyeka offers stable output (1.73 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Onyeka offers stable output (1.73 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -18290,7 +18290,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>Rushworth offers stable output (3.41 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Rushworth offers stable output (3.41 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>Dovin offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dovin carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: not included in squad.; Low defensive odds; clean sheet unlikely (23.9%); Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>Wilson offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Wilson offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>Thomas carries elevated risk for GW7 (3.17 exp pts). Concerns: Low defensive odds; clean sheet unlikely (23.9%); Tough offensive matchup (FDR: 1.0)</t>
+          <t>Thomas carries elevated risk for GW8 (3.17 exp pts). Concerns: Low defensive odds; clean sheet unlikely (23.9%); Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>Kitching offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kitching carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Sheffield United on loan for the rest of the season; Low defensive odds; clean sheet unlikely (23.9%); Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>van Ewijk offers stable output (2.31 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>van Ewijk offers stable output (2.31 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>Dasilva offers stable output (2.99 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dasilva offers stable output (2.99 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -18920,7 +18920,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>Kesler-Hayden offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kesler-Hayden offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -19010,7 +19010,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>Bidwell offers stable output (0.21 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bidwell offers stable output (0.21 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>Latibeaudiere offers stable output (0.17 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Latibeaudiere offers stable output (0.17 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -19128,7 +19128,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -19190,7 +19190,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>Woolfenden offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Woolfenden carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Low defensive odds; clean sheet unlikely (23.9%); Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>Brau offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Brau carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Academico de Viseu on loan for the rest of the season; Low defensive odds; clean sheet unlikely (23.9%); Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -19308,7 +19308,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>Amenda offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Amenda carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Calf injury - Unknown return date; Low defensive odds; clean sheet unlikely (23.9%); Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -19460,7 +19460,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>Rudoni offers stable output (3.29 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Rudoni offers stable output (3.29 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -19550,7 +19550,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>Grimes offers stable output (2.81 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Grimes offers stable output (2.81 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -19640,7 +19640,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>Sakamoto offers stable output (0.88 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Sakamoto offers stable output (0.88 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>Mason-Clark offers stable output (1.48 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mason-Clark offers stable output (1.48 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -19758,7 +19758,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>Eccles offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Eccles carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Ankle injury - Unknown return date; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>Torp offers stable output (0.56 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Torp offers stable output (0.56 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>Shepherd offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Shepherd offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -20090,7 +20090,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>Tchaouna offers stable output (1.17 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tchaouna offers stable output (1.17 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -20180,7 +20180,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>Borges Rodrigues offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Borges Rodrigues carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Burton Albion on loan for the rest of the season; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -20270,7 +20270,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>Andrews offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Andrews carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Oxford United on loan for the rest of the season; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -20360,7 +20360,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>Wright offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Wright carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Thigh injury - Unknown return date; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -20450,7 +20450,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>Thomas-Asante offers stable output (2.51 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Thomas-Asante offers stable output (2.51 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -20540,7 +20540,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>Simms offers stable output (1.01 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Simms offers stable output (1.01 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -20568,7 +20568,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -20630,7 +20630,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>Markelo offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Markelo carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Shabab Al-Ahli Dubai permanently; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -20658,7 +20658,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -20720,7 +20720,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>Bassette offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bassette carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined KVC Westerlo on loan for the rest of the season; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>Awoniyi offers stable output (1.30 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Awoniyi offers stable output (1.30 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -20900,7 +20900,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>Yirenkyi offers stable output (1.91 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Yirenkyi offers stable output (1.91 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -20990,7 +20990,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>Hamer offers stable output (0.49 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hamer offers stable output (0.49 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>Cherif carries elevated risk for GW7 (1.17 exp pts). Concerns: Rotation risk (only 13% projected start); Regression warning: projected PPG is -3.97 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
+          <t>Cherif carries elevated risk for GW8 (1.17 exp pts). Concerns: Rotation risk (only 13% projected start); Regression warning: projected PPG is -3.97 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -21170,7 +21170,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>Bentley offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bentley offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>Gboho offers stable output (0.60 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gboho offers stable output (0.60 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>Mfuni carries elevated risk for GW7 (0.52 exp pts). Concerns: Rotation risk (only 7% projected start); Low defensive odds; clean sheet unlikely (23.9%); Regression warning: projected PPG is -6.18 lower than past form</t>
+          <t>Mfuni carries elevated risk for GW8 (0.52 exp pts). Concerns: Rotation risk (only 7% projected start); Low defensive odds; clean sheet unlikely (23.9%); Regression warning: projected PPG is -6.18 lower than past form</t>
         </is>
       </c>
     </row>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>Guessand offers stable output (0.03 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Guessand offers stable output (0.03 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -21530,7 +21530,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>Disasi offers stable output (0.38 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Disasi offers stable output (0.38 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -21558,7 +21558,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>Henderson offers stable output (0.61 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Henderson carries elevated risk for GW8 (0.61 exp pts). Concerns: Injury doubt: Foot injury - 50% chance of playing; Low defensive odds; clean sheet unlikely (22.2%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -21710,7 +21710,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>Benitez offers stable output (2.08 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Benitez offers stable output (2.08 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -21800,7 +21800,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>Richards offers stable output (2.40 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Richards offers stable output (2.40 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>Canvot offers stable output (2.51 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Canvot offers stable output (2.51 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -21980,7 +21980,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>Mitchell offers stable output (3.12 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mitchell offers stable output (3.12 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -22008,7 +22008,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -22070,7 +22070,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>Sosa offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Sosa carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined FC Cologne on loan for the rest of the season; Low defensive odds; clean sheet unlikely (22.2%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -22098,7 +22098,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -22160,7 +22160,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>Chadi Riad offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Chadi Riad carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Low defensive odds; clean sheet unlikely (22.2%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>Mingueza offers stable output (0.36 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mingueza offers stable output (0.36 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -22340,7 +22340,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>Sarr carries elevated risk for GW7 (0.01 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 0.9)</t>
+          <t>Sarr carries elevated risk for GW8 (0.01 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -22430,7 +22430,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>Wharton offers stable output (3.11 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Wharton offers stable output (3.11 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -22520,7 +22520,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>Yeremy offers stable output (2.52 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Yeremy offers stable output (2.52 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>Hughes offers stable output (0.23 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hughes offers stable output (0.23 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>Lerma offers stable output (0.27 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lerma offers stable output (0.27 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>Kamada carries elevated risk for GW7 (3.06 exp pts). Concerns: Regression warning: projected PPG is -1.39 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Kamada carries elevated risk for GW8 (3.06 exp pts). Concerns: Regression warning: projected PPG is -1.39 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -22818,7 +22818,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>Devenny offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Devenny carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Stoke City permanently; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>Esse offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Esse carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Millwall on loan for the rest of the season; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -22998,7 +22998,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -23060,7 +23060,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>M.França offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>M.França carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Alverca on loan for the rest of the season; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -23150,7 +23150,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>Doucouré offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Doucouré offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>J.Rak-Sakyi offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>J.Rak-Sakyi carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: has joined  Kasimpasa on loan for the rest of the seaon.; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -23268,7 +23268,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -23330,7 +23330,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>Cardines offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Cardines carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Bristol City on loan for the rest of the season; Low defensive odds; clean sheet unlikely (22.2%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -23420,7 +23420,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>Drakes-Thomas offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Drakes-Thomas offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>Strand Larsen offers stable output (3.25 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Strand Larsen offers stable output (3.25 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -23600,7 +23600,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>Mateta carries elevated risk for GW7 (1.14 exp pts). Concerns: Rotation risk (only 7% projected start); Tough offensive matchup (FDR: 0.9)</t>
+          <t>Mateta carries elevated risk for GW8 (1.14 exp pts). Concerns: Rotation risk (only 7% projected start); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -23690,7 +23690,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>Nketiah offers stable output (1.48 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Nketiah offers stable output (1.48 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -23780,7 +23780,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>Uche offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Uche carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: has returned to Getafe CF; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -23870,7 +23870,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>McNeil offers stable output (0.88 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>McNeil offers stable output (0.88 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -23960,7 +23960,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>Matthews offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Matthews offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -23988,7 +23988,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -24050,7 +24050,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>Tomiyasu offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tomiyasu carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Calf injury - Expected back 8 Nov; Low defensive odds; clean sheet unlikely (22.2%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -24140,7 +24140,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>Khalaili offers stable output (3.16 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Khalaili offers stable output (3.16 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>Gozo offers stable output (0.58 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gozo offers stable output (0.58 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -24320,7 +24320,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>Ahanor offers stable output (0.61 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ahanor offers stable output (0.61 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -24410,7 +24410,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>Chilwell carries elevated risk for GW7 (0.36 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (22.2%); Regression warning: projected PPG is -3.92 lower than past form</t>
+          <t>Chilwell carries elevated risk for GW8 (0.36 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (22.2%); Regression warning: projected PPG is -3.92 lower than past form</t>
         </is>
       </c>
     </row>
@@ -24438,7 +24438,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -24500,7 +24500,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>Timber offers stable output (1.82 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Timber carries elevated risk for GW8 (1.82 exp pts). Concerns: Injury doubt: Hamstring injury - 75% chance of playing; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>Osorio offers stable output (0.61 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Osorio offers stable output (0.61 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -24680,7 +24680,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>Nørgaard offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Nørgaard offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -24770,7 +24770,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>Johnson offers stable output (1.21 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Johnson offers stable output (1.21 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -24860,7 +24860,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>Pickford offers stable output (2.85 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Pickford offers stable output (2.85 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>Travers offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Travers offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -25040,7 +25040,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>King offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>King offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>Tarkowski carries elevated risk for GW7 (2.57 exp pts). Concerns: Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -3.44 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Tarkowski carries elevated risk for GW8 (2.57 exp pts). Concerns: Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -3.44 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -25220,7 +25220,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>Branthwaite carries elevated risk for GW7 (2.25 exp pts). Concerns: Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -1.62 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Branthwaite carries elevated risk for GW8 (2.25 exp pts). Concerns: Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -1.62 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -25310,7 +25310,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>Keane offers stable output (0.43 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Keane offers stable output (0.43 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -25400,7 +25400,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>O'Brien offers stable output (0.22 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>O'Brien offers stable output (0.22 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -25490,7 +25490,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>Mykolenko carries elevated risk for GW7 (2.23 exp pts). Concerns: Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -1.90 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Mykolenko carries elevated risk for GW8 (2.23 exp pts). Concerns: Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -1.90 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -25518,7 +25518,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -25580,7 +25580,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>Patterson offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Patterson carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Torino permanently; Low defensive odds; clean sheet unlikely (18.2%); Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -25608,7 +25608,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>Aznou offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Aznou carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Malaga on loan for the rest of the season; Low defensive odds; clean sheet unlikely (18.2%); Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -25760,7 +25760,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>Dewsbury-Hall carries elevated risk for GW7 (3.55 exp pts). Concerns: Regression warning: projected PPG is -1.21 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Dewsbury-Hall carries elevated risk for GW8 (3.55 exp pts). Concerns: Regression warning: projected PPG is -1.21 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -25850,7 +25850,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>Grealish carries elevated risk for GW7 (1.17 exp pts). Concerns: Rotation risk (only 24% projected start); Tough offensive matchup (FDR: 1.4)</t>
+          <t>Grealish carries elevated risk for GW8 (1.17 exp pts). Concerns: Rotation risk (only 24% projected start); Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -25940,7 +25940,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>Garner carries elevated risk for GW7 (2.39 exp pts). Concerns: Rotation risk (only 68% projected start); Tough offensive matchup (FDR: 1.4)</t>
+          <t>Garner carries elevated risk for GW8 (2.39 exp pts). Concerns: Rotation risk (only 68% projected start); Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -26030,7 +26030,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>George offers stable output (2.25 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>George offers stable output (2.25 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -26120,7 +26120,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>Alcaraz offers stable output (0.01 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Alcaraz offers stable output (0.01 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -26210,7 +26210,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>Armstrong offers stable output (2.43 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Armstrong offers stable output (2.43 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -26300,7 +26300,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>Dibling offers stable output (0.35 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dibling offers stable output (0.35 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>Röhl offers stable output (1.48 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Röhl offers stable output (1.48 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -26480,7 +26480,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>Hackney offers stable output (0.64 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hackney offers stable output (0.64 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -26508,7 +26508,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -26570,7 +26570,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>Beto offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Beto carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Fiorentina permanently; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -26660,7 +26660,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>Barry offers stable output (3.48 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Barry offers stable output (3.48 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>Maitland-Niles carries elevated risk for GW7 (1.06 exp pts). Concerns: Rotation risk (only 24% projected start); Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -4.25 lower than past form</t>
+          <t>Maitland-Niles carries elevated risk for GW8 (1.06 exp pts). Concerns: Rotation risk (only 24% projected start); Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -4.25 lower than past form</t>
         </is>
       </c>
     </row>
@@ -26840,7 +26840,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>Graham offers stable output (0.52 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Graham offers stable output (0.52 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -26930,7 +26930,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>Leno offers stable output (3.78 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Leno offers stable output (3.78 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -27020,7 +27020,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>Lecomte offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lecomte offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -27048,7 +27048,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -27110,7 +27110,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>McNally offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>McNally carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined York City on loan for the rest of the season; Tough offensive matchup (FDR: 1.5)</t>
         </is>
       </c>
     </row>
@@ -27200,7 +27200,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>Andersen offers stable output (0.65 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Andersen offers stable output (0.65 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -27290,7 +27290,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>Robinson offers stable output (2.86 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Robinson offers stable output (2.86 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -27380,7 +27380,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>J.Cuenca offers stable output (0.46 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>J.Cuenca offers stable output (0.46 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -27470,7 +27470,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>Tete offers stable output (0.43 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tete offers stable output (0.43 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -27560,7 +27560,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>Bassey offers stable output (2.79 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bassey offers stable output (2.79 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -27650,7 +27650,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>Castagne carries elevated risk for GW7 (2.77 exp pts). Concerns: Rotation risk (only 67% projected start); Regression warning: projected PPG is -2.00 lower than past form; Tough offensive matchup (FDR: 1.5)</t>
+          <t>Castagne carries elevated risk for GW8 (2.77 exp pts). Concerns: Rotation risk (only 67% projected start); Regression warning: projected PPG is -2.00 lower than past form; Tough offensive matchup (FDR: 1.5)</t>
         </is>
       </c>
     </row>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>Iwobi is projected for 4.27 pts in GW7 and 19.9 pts over next 5 weeks. Key drivers: Nailed starter (92% expected start probability); Primary creative playmaker (0.36 xA per 90)</t>
+          <t>Iwobi is projected for 4.27 pts in GW8 and 19.9 pts over next 5 weeks. Key drivers: Nailed starter (92% expected start probability); Primary creative playmaker (0.36 xA per 90)</t>
         </is>
       </c>
     </row>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>Smith Rowe offers stable output (0.64 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Smith Rowe offers stable output (0.64 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -27920,7 +27920,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>Kevin offers stable output (0.84 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kevin offers stable output (0.84 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -28010,7 +28010,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>Bobb offers stable output (3.36 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bobb offers stable output (3.36 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>Berge offers stable output (2.79 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Berge offers stable output (2.79 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -28190,7 +28190,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>Cairney offers stable output (0.35 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Cairney offers stable output (0.35 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -28280,7 +28280,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>King offers stable output (3.78 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>King offers stable output (3.78 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -28308,7 +28308,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -28370,7 +28370,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>Sessegnon offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Sessegnon carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Suspended until 7 Nov; Tough offensive matchup (FDR: 1.5)</t>
         </is>
       </c>
     </row>
@@ -28460,7 +28460,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>Reed offers stable output (0.24 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Reed offers stable output (0.24 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>Muniz offers stable output (0.03 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Muniz offers stable output (0.03 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -28640,7 +28640,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>Kusi-Asare offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kusi-Asare offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -28730,7 +28730,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>Gonzalo offers stable output (3.78 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gonzalo offers stable output (3.78 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -28820,7 +28820,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>Palacios offers stable output (0.73 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Palacios offers stable output (0.73 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>Charles offers stable output (2.66 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Charles offers stable output (2.66 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -29000,7 +29000,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>De Fougerolles offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>De Fougerolles carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: has joined  Real Salt Lake on loan for the rest of the seaon.; Tough offensive matchup (FDR: 1.5)</t>
         </is>
       </c>
     </row>
@@ -29090,7 +29090,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>Zepa offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Zepa offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -29118,7 +29118,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -29180,7 +29180,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>Larsson offers stable output (0.27 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Larsson carries elevated risk for GW8 (0.27 exp pts). Concerns: Injury doubt: Groin injury - 25% chance of playing; Tough offensive matchup (FDR: 1.5)</t>
         </is>
       </c>
     </row>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>Ángel offers stable output (0.01 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ángel offers stable output (0.01 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -29360,7 +29360,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>Affengruber carries elevated risk for GW7 (1.77 exp pts). Concerns: Rotation risk (only 48% projected start); Regression warning: projected PPG is -3.57 lower than past form; Tough offensive matchup (FDR: 1.5)</t>
+          <t>Affengruber carries elevated risk for GW8 (1.77 exp pts). Concerns: Rotation risk (only 48% projected start); Regression warning: projected PPG is -3.57 lower than past form; Tough offensive matchup (FDR: 1.5)</t>
         </is>
       </c>
     </row>
@@ -29450,7 +29450,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>Iroegbunam offers stable output (0.42 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Iroegbunam offers stable output (0.42 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -29540,7 +29540,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>Phillips offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Phillips offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -29568,7 +29568,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -29630,7 +29630,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>Butland offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Butland carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Arm injury - Unknown return date; Low defensive odds; clean sheet unlikely (19.3%); Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -29720,7 +29720,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>Cartwright offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Cartwright carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Grimsby Town on loan for the rest of the season; Low defensive odds; clean sheet unlikely (19.3%); Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -29748,7 +29748,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -29810,7 +29810,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>Lo-Tutala offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lo-Tutala carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Colchester United on loan for the rest of the season; Low defensive odds; clean sheet unlikely (19.3%); Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -29900,7 +29900,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>Egan carries elevated risk for GW7 (2.27 exp pts). Concerns: Low defensive odds; clean sheet unlikely (19.3%); Regression warning: projected PPG is -1.74 lower than past form; Tough offensive matchup (FDR: 0.7)</t>
+          <t>Egan carries elevated risk for GW8 (2.27 exp pts). Concerns: Low defensive odds; clean sheet unlikely (19.3%); Regression warning: projected PPG is -1.74 lower than past form; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -29928,7 +29928,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -29990,7 +29990,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>Hughes offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hughes carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Groin injury - Unknown return date; Low defensive odds; clean sheet unlikely (19.3%); Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -30080,7 +30080,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>Ajayi carries elevated risk for GW7 (2.47 exp pts). Concerns: Low defensive odds; clean sheet unlikely (19.3%); Regression warning: projected PPG is -1.35 lower than past form; Tough offensive matchup (FDR: 0.7)</t>
+          <t>Ajayi carries elevated risk for GW8 (2.47 exp pts). Concerns: Low defensive odds; clean sheet unlikely (19.3%); Regression warning: projected PPG is -1.35 lower than past form; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -30170,7 +30170,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>Coyle offers stable output (2.14 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Coyle offers stable output (2.14 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -30198,7 +30198,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -30260,7 +30260,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>Drameh offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Drameh carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Genoa permanently; Low defensive odds; clean sheet unlikely (19.3%); Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -30350,7 +30350,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>Giles offers stable output (2.39 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Giles offers stable output (2.39 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -30378,7 +30378,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -30440,7 +30440,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>Jacob offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Jacob carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Newport County on loan until January; Low defensive odds; clean sheet unlikely (19.3%); Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -30530,7 +30530,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>McCarthy offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>McCarthy offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -30620,7 +30620,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>McNair offers stable output (0.26 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>McNair offers stable output (0.26 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>Belloumi carries elevated risk for GW7 (3.25 exp pts). Concerns: Rotation risk (only 68% projected start); Regression warning: projected PPG is -2.62 lower than past form; Tough offensive matchup (FDR: 0.7)</t>
+          <t>Belloumi carries elevated risk for GW8 (3.25 exp pts). Concerns: Rotation risk (only 68% projected start); Regression warning: projected PPG is -2.62 lower than past form; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -30738,7 +30738,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -30800,7 +30800,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>Millar offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Millar carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Birmingham on loan for the rest of the season; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -30890,7 +30890,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>Dowell offers stable output (0.38 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dowell offers stable output (0.38 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -30980,7 +30980,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>Crooks offers stable output (1.51 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Crooks offers stable output (1.51 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -31070,7 +31070,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>Slater offers stable output (2.62 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Slater offers stable output (2.62 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -31098,7 +31098,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>Matazo offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Matazo carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>Ömür offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ömür offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -31278,7 +31278,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -31340,7 +31340,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>Kamara offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kamara carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Portsmouth permanently; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>Zambrano offers stable output (0.30 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Zambrano offers stable output (0.30 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -31520,7 +31520,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>McBurnie offers stable output (2.64 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>McBurnie offers stable output (2.64 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -31548,7 +31548,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>Akintola offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Akintola carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Omonoia FC permanently; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -31638,7 +31638,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -31700,7 +31700,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>Gyabi offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gyabi carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Thigh injury - Unknown return date; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -31728,7 +31728,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -31790,7 +31790,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>Destan offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Destan carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Konyaspor permanently; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -31818,7 +31818,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -31880,7 +31880,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>Burstow offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Burstow carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Sheffield Wednesday on loan for the rest of the season; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -31970,7 +31970,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>Gelhardt offers stable output (0.96 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gelhardt offers stable output (0.96 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -31998,7 +31998,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G351" t="n">
@@ -32060,7 +32060,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>Targett offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Targett carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Ankle injury - Unknown return date; Low defensive odds; clean sheet unlikely (19.3%); Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>Morita offers stable output (0.47 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Morita offers stable output (0.47 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -32240,7 +32240,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>Tzolakis carries elevated risk for GW7 (3.63 exp pts). Concerns: Low defensive odds; clean sheet unlikely (19.3%); Regression warning: projected PPG is -1.52 lower than past form; Tough offensive matchup (FDR: 0.7)</t>
+          <t>Tzolakis carries elevated risk for GW8 (3.63 exp pts). Concerns: Low defensive odds; clean sheet unlikely (19.3%); Regression warning: projected PPG is -1.52 lower than past form; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -32330,7 +32330,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>Hjertø-Dahl offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hjertø-Dahl offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -32420,7 +32420,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>Stroud offers stable output (1.19 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Stroud offers stable output (1.19 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -32510,7 +32510,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>Herrington offers stable output (0.72 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Herrington offers stable output (0.72 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -32600,7 +32600,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>Mendy carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (19.3%); Regression warning: projected PPG is -4.52 lower than past form</t>
+          <t>Mendy carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Groin injury - Expected back 31 Oct; Low defensive odds; clean sheet unlikely (19.3%); Regression warning: projected PPG is -4.52 lower than past form</t>
         </is>
       </c>
     </row>
@@ -32628,7 +32628,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -32690,7 +32690,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>Gourna-Douath offers stable output (0.31 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gourna-Douath carries elevated risk for GW8 (0.31 exp pts). Concerns: Injury doubt: Calf injury - 50% chance of playing; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -32718,7 +32718,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -32780,7 +32780,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>Cho offers stable output (0.81 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Cho carries elevated risk for GW8 (0.81 exp pts). Concerns: Injury doubt: Unspecified injury - 50% chance of playing; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -32808,7 +32808,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -32870,7 +32870,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>Ansah offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ansah carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Back injury - Unknown return date; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -32898,7 +32898,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G361" t="n">
@@ -32960,7 +32960,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>Vaz offers stable output (0.53 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Vaz carries elevated risk for GW8 (0.53 exp pts). Concerns: Injury doubt: Achilles injury - 75% chance of playing; Tough offensive matchup (FDR: 0.7)</t>
         </is>
       </c>
     </row>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>Norton-Cuffy offers stable output (0.37 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Norton-Cuffy offers stable output (0.37 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -33140,7 +33140,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>Thomas offers stable output (1.36 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Thomas offers stable output (1.36 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -33230,7 +33230,7 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>Mouzakitis offers stable output (0.18 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mouzakitis offers stable output (0.18 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>Diop offers stable output (2.58 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Diop offers stable output (2.58 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -33348,7 +33348,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G366" t="n">
@@ -33410,7 +33410,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>Lukić offers stable output (1.60 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lukić carries elevated risk for GW8 (1.60 exp pts). Concerns: Injury doubt: Groin injury - 75% chance of playing; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>Walton offers stable output (0.81 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Walton offers stable output (0.81 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>Palmer offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Palmer offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -33680,7 +33680,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>Button offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Button offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -33770,7 +33770,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>Kipré offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kipré offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -33860,7 +33860,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>O'Shea offers stable output (2.96 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>O'Shea offers stable output (2.96 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -33950,7 +33950,7 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>Davis offers stable output (3.05 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Davis offers stable output (3.05 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -34040,7 +34040,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>Greaves offers stable output (2.09 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Greaves offers stable output (2.09 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -34068,7 +34068,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G374" t="n">
@@ -34130,7 +34130,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>Johnson offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Johnson carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Stoke City on loan for the rest of the season; Low defensive odds; clean sheet unlikely (23.5%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -34220,7 +34220,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>Furlong offers stable output (0.22 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Furlong offers stable output (0.22 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>Núñez offers stable output (0.41 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Núñez offers stable output (0.41 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -34400,7 +34400,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>Matusiwa offers stable output (0.20 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Matusiwa offers stable output (0.20 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -34428,7 +34428,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G378" t="n">
@@ -34490,7 +34490,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>Burns offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Burns carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Leicester City permanently; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -34580,7 +34580,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>Taylor offers stable output (0.31 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Taylor offers stable output (0.31 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -34670,7 +34670,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>Clarke offers stable output (1.16 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Clarke offers stable output (1.16 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -34698,7 +34698,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -34760,7 +34760,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>Ogbene offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ogbene carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Lincoln City on loan until January; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -34850,7 +34850,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>Fatawu offers stable output (1.46 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Fatawu offers stable output (1.46 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -34940,7 +34940,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>Emersonn carries elevated risk for GW7 (3.48 exp pts). Concerns: Rotation risk (only 62% projected start); Tough offensive matchup (FDR: 0.9)</t>
+          <t>Emersonn carries elevated risk for GW8 (3.48 exp pts). Concerns: Rotation risk (only 62% projected start); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -34968,7 +34968,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G384" t="n">
@@ -35030,7 +35030,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>Hirst offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hirst carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Stoke City permanently; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -35120,7 +35120,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>Philogene offers stable output (0.34 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Philogene offers stable output (0.34 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -35148,7 +35148,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G386" t="n">
@@ -35210,7 +35210,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>Szmodics offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Szmodics carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Derby County on loan for the rest of the season; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -35300,7 +35300,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>Akpom offers stable output (0.89 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Akpom offers stable output (0.89 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>Walle Egeli offers stable output (0.41 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Walle Egeli offers stable output (0.41 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -35418,7 +35418,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G389" t="n">
@@ -35480,7 +35480,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>Al-Hamadi offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Al-Hamadi carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Sheffield Wednesday on loan for the rest of the season; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -35570,7 +35570,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>McAteer offers stable output (0.51 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>McAteer offers stable output (0.51 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -35660,7 +35660,7 @@
       </c>
       <c r="Z391" t="inlineStr">
         <is>
-          <t>Mehmeti offers stable output (0.65 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mehmeti offers stable output (0.65 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -35688,7 +35688,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G392" t="n">
@@ -35750,7 +35750,7 @@
       </c>
       <c r="Z392" t="inlineStr">
         <is>
-          <t>Van Oevelen offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Van Oevelen carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Valencia on loan for the rest of the season; Low defensive odds; clean sheet unlikely (23.5%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -35840,7 +35840,7 @@
       </c>
       <c r="Z393" t="inlineStr">
         <is>
-          <t>Maeda offers stable output (2.72 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Maeda offers stable output (2.72 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -35930,7 +35930,7 @@
       </c>
       <c r="Z394" t="inlineStr">
         <is>
-          <t>Scherpen offers stable output (2.05 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Scherpen offers stable output (2.05 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="Z395" t="inlineStr">
         <is>
-          <t>Florentino offers stable output (0.47 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Florentino offers stable output (0.47 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -36110,7 +36110,7 @@
       </c>
       <c r="Z396" t="inlineStr">
         <is>
-          <t>Enciso offers stable output (3.39 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Enciso offers stable output (3.39 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -36200,7 +36200,7 @@
       </c>
       <c r="Z397" t="inlineStr">
         <is>
-          <t>Ouattara offers stable output (0.82 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ouattara offers stable output (0.82 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -36228,7 +36228,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G398" t="n">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="Z398" t="inlineStr">
         <is>
-          <t>Humphreys offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Humphreys carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Huddersfield Town on loan for the rest of the season; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -36380,7 +36380,7 @@
       </c>
       <c r="Z399" t="inlineStr">
         <is>
-          <t>Palacios offers stable output (2.06 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Palacios offers stable output (2.06 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -36470,7 +36470,7 @@
       </c>
       <c r="Z400" t="inlineStr">
         <is>
-          <t>Flemming offers stable output (0.93 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Flemming offers stable output (0.93 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -36560,7 +36560,7 @@
       </c>
       <c r="Z401" t="inlineStr">
         <is>
-          <t>Wilson carries elevated risk for GW7 (0.35 exp pts). Concerns: Rotation risk (only 13% projected start); Tough offensive matchup (FDR: 1.1)</t>
+          <t>Wilson carries elevated risk for GW8 (0.35 exp pts). Concerns: Rotation risk (only 13% projected start); Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -36588,7 +36588,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G402" t="n">
@@ -36650,7 +36650,7 @@
       </c>
       <c r="Z402" t="inlineStr">
         <is>
-          <t>Perri offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Perri carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Torino on loan for the rest of the season; Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -36740,7 +36740,7 @@
       </c>
       <c r="Z403" t="inlineStr">
         <is>
-          <t>Bijol offers stable output (0.71 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bijol offers stable output (0.71 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -36768,7 +36768,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G404" t="n">
@@ -36830,7 +36830,7 @@
       </c>
       <c r="Z404" t="inlineStr">
         <is>
-          <t>Rodon offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Rodon carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Expected back 21 Nov; Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -36920,7 +36920,7 @@
       </c>
       <c r="Z405" t="inlineStr">
         <is>
-          <t>Bogle offers stable output (4.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bogle offers stable output (4.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -37010,7 +37010,7 @@
       </c>
       <c r="Z406" t="inlineStr">
         <is>
-          <t>Gudmundsson offers stable output (2.15 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gudmundsson offers stable output (2.15 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -37100,7 +37100,7 @@
       </c>
       <c r="Z407" t="inlineStr">
         <is>
-          <t>Justin carries elevated risk for GW7 (3.62 exp pts). Concerns: Regression warning: projected PPG is -1.56 lower than past form; Tough offensive matchup (FDR: 1.1)</t>
+          <t>Justin carries elevated risk for GW8 (3.62 exp pts). Concerns: Regression warning: projected PPG is -1.56 lower than past form; Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -37128,7 +37128,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G408" t="n">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="Z408" t="inlineStr">
         <is>
-          <t>Bornauw offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bornauw carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Hamburg SV on loan for the rest of the season; Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -37280,7 +37280,7 @@
       </c>
       <c r="Z409" t="inlineStr">
         <is>
-          <t>Muharemović carries elevated risk for GW7 (3.17 exp pts). Concerns: Regression warning: projected PPG is -1.90 lower than past form; Tough offensive matchup (FDR: 1.1)</t>
+          <t>Muharemović carries elevated risk for GW8 (3.17 exp pts). Concerns: Regression warning: projected PPG is -1.90 lower than past form; Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -37370,7 +37370,7 @@
       </c>
       <c r="Z410" t="inlineStr">
         <is>
-          <t>Stach offers stable output (3.73 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Stach offers stable output (3.73 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="Z411" t="inlineStr">
         <is>
-          <t>Okafor offers stable output (2.87 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Okafor offers stable output (2.87 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -37550,7 +37550,7 @@
       </c>
       <c r="Z412" t="inlineStr">
         <is>
-          <t>Aaronson offers stable output (1.06 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Aaronson offers stable output (1.06 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -37640,7 +37640,7 @@
       </c>
       <c r="Z413" t="inlineStr">
         <is>
-          <t>Ampadu offers stable output (2.60 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ampadu offers stable output (2.60 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -37730,7 +37730,7 @@
       </c>
       <c r="Z414" t="inlineStr">
         <is>
-          <t>Longstaff offers stable output (0.33 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Longstaff offers stable output (0.33 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G415" t="n">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="Z415" t="inlineStr">
         <is>
-          <t>Gnonto offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gnonto carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined ACF Fiorentina on loan for the rest of the season; Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -37848,7 +37848,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G416" t="n">
@@ -37910,7 +37910,7 @@
       </c>
       <c r="Z416" t="inlineStr">
         <is>
-          <t>Harrison offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Harrison carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined New England Revolution permanently; Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -37938,7 +37938,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G417" t="n">
@@ -38000,7 +38000,7 @@
       </c>
       <c r="Z417" t="inlineStr">
         <is>
-          <t>James offers stable output (0.58 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>James carries elevated risk for GW8 (0.58 exp pts). Concerns: Injury doubt: Back injury - 50% chance of playing; Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -38090,7 +38090,7 @@
       </c>
       <c r="Z418" t="inlineStr">
         <is>
-          <t>Gruev offers stable output (0.18 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gruev offers stable output (0.18 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -38180,7 +38180,7 @@
       </c>
       <c r="Z419" t="inlineStr">
         <is>
-          <t>Tanaka offers stable output (1.96 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tanaka offers stable output (1.96 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -38270,7 +38270,7 @@
       </c>
       <c r="Z420" t="inlineStr">
         <is>
-          <t>Calvert-Lewin offers stable output (3.98 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Calvert-Lewin offers stable output (3.98 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -38360,7 +38360,7 @@
       </c>
       <c r="Z421" t="inlineStr">
         <is>
-          <t>Nmecha offers stable output (0.89 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Nmecha offers stable output (0.89 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -38388,7 +38388,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G422" t="n">
@@ -38450,7 +38450,7 @@
       </c>
       <c r="Z422" t="inlineStr">
         <is>
-          <t>Piroe offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Piroe carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined West Ham United on loan for the rest of the season; Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -38478,7 +38478,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G423" t="n">
@@ -38540,7 +38540,7 @@
       </c>
       <c r="Z423" t="inlineStr">
         <is>
-          <t>Mateo Joseph offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mateo Joseph carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -38630,7 +38630,7 @@
       </c>
       <c r="Z424" t="inlineStr">
         <is>
-          <t>Trafford is projected for 4.50 pts in GW7 and 21.5 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); Strong save volume floor (3.7 saves/90)</t>
+          <t>Trafford is projected for 4.50 pts in GW8 and 21.5 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); Strong save volume floor (3.7 saves/90)</t>
         </is>
       </c>
     </row>
@@ -38720,7 +38720,7 @@
       </c>
       <c r="Z425" t="inlineStr">
         <is>
-          <t>Elvedi offers stable output (2.88 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Elvedi offers stable output (2.88 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -38810,7 +38810,7 @@
       </c>
       <c r="Z426" t="inlineStr">
         <is>
-          <t>Lienou offers stable output (0.17 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lienou offers stable output (0.17 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -38900,7 +38900,7 @@
       </c>
       <c r="Z427" t="inlineStr">
         <is>
-          <t>Cresswell offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Cresswell offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -38990,7 +38990,7 @@
       </c>
       <c r="Z428" t="inlineStr">
         <is>
-          <t>Cairns offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Cairns offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -39080,7 +39080,7 @@
       </c>
       <c r="Z429" t="inlineStr">
         <is>
-          <t>Zetterer offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Zetterer offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -39170,7 +39170,7 @@
       </c>
       <c r="Z430" t="inlineStr">
         <is>
-          <t>Bard offers stable output (0.21 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bard offers stable output (0.21 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -39260,7 +39260,7 @@
       </c>
       <c r="Z431" t="inlineStr">
         <is>
-          <t>Bahoya offers stable output (0.53 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bahoya offers stable output (0.53 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -39350,7 +39350,7 @@
       </c>
       <c r="Z432" t="inlineStr">
         <is>
-          <t>A.Becker offers stable output (3.61 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>A.Becker offers stable output (3.61 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -39440,7 +39440,7 @@
       </c>
       <c r="Z433" t="inlineStr">
         <is>
-          <t>Mamardashvili offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mamardashvili offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -39530,7 +39530,7 @@
       </c>
       <c r="Z434" t="inlineStr">
         <is>
-          <t>Woodman offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Woodman offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -39558,7 +39558,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G435" t="n">
@@ -39620,7 +39620,7 @@
       </c>
       <c r="Z435" t="inlineStr">
         <is>
-          <t>Pecsi offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Pecsi carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined TSV Hartberg on loan for the rest of the season; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -39648,7 +39648,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G436" t="n">
@@ -39710,7 +39710,7 @@
       </c>
       <c r="Z436" t="inlineStr">
         <is>
-          <t>Jaros offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Jaros carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -39800,7 +39800,7 @@
       </c>
       <c r="Z437" t="inlineStr">
         <is>
-          <t>Davies offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Davies offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -39890,7 +39890,7 @@
       </c>
       <c r="Z438" t="inlineStr">
         <is>
-          <t>Virgil carries elevated risk for GW7 (2.55 exp pts). Concerns: Regression warning: projected PPG is -1.51 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
+          <t>Virgil carries elevated risk for GW8 (2.55 exp pts). Concerns: Regression warning: projected PPG is -1.51 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -39918,7 +39918,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G439" t="n">
@@ -39980,7 +39980,7 @@
       </c>
       <c r="Z439" t="inlineStr">
         <is>
-          <t>Frimpong offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Frimpong carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Unknown return date; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -40070,7 +40070,7 @@
       </c>
       <c r="Z440" t="inlineStr">
         <is>
-          <t>Kerkez offers stable output (2.44 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kerkez offers stable output (2.44 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -40160,7 +40160,7 @@
       </c>
       <c r="Z441" t="inlineStr">
         <is>
-          <t>Gomez offers stable output (0.20 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gomez offers stable output (0.20 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -40188,7 +40188,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G442" t="n">
@@ -40250,7 +40250,7 @@
       </c>
       <c r="Z442" t="inlineStr">
         <is>
-          <t>Bradley offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bradley carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -40340,7 +40340,7 @@
       </c>
       <c r="Z443" t="inlineStr">
         <is>
-          <t>Lucky offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lucky offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -40430,7 +40430,7 @@
       </c>
       <c r="Z444" t="inlineStr">
         <is>
-          <t>Jacquet carries elevated risk for GW7 (2.79 exp pts). Concerns: Regression warning: projected PPG is -1.41 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
+          <t>Jacquet carries elevated risk for GW8 (2.79 exp pts). Concerns: Regression warning: projected PPG is -1.41 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -40458,7 +40458,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G445" t="n">
@@ -40520,7 +40520,7 @@
       </c>
       <c r="Z445" t="inlineStr">
         <is>
-          <t>Leoni offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Leoni carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -40610,7 +40610,7 @@
       </c>
       <c r="Z446" t="inlineStr">
         <is>
-          <t>Tsimikas offers stable output (0.25 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tsimikas offers stable output (0.25 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -40638,7 +40638,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G447" t="n">
@@ -40700,7 +40700,7 @@
       </c>
       <c r="Z447" t="inlineStr">
         <is>
-          <t>Ramsay offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ramsay carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined St Mirren on loan for the rest of the season; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -40790,7 +40790,7 @@
       </c>
       <c r="Z448" t="inlineStr">
         <is>
-          <t>Wirtz offers stable output (3.44 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Wirtz offers stable output (3.44 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -40880,7 +40880,7 @@
       </c>
       <c r="Z449" t="inlineStr">
         <is>
-          <t>Gakpo carries elevated risk for GW7 (3.15 exp pts). Concerns: Rotation risk (only 49% projected start); Regression warning: projected PPG is -3.86 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
+          <t>Gakpo carries elevated risk for GW8 (3.15 exp pts). Concerns: Rotation risk (only 49% projected start); Regression warning: projected PPG is -3.86 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -40908,7 +40908,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G450" t="n">
@@ -40970,7 +40970,7 @@
       </c>
       <c r="Z450" t="inlineStr">
         <is>
-          <t>Szoboszlai carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.3)</t>
+          <t>Szoboszlai carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Unknown return date; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -41060,7 +41060,7 @@
       </c>
       <c r="Z451" t="inlineStr">
         <is>
-          <t>Ngumoha offers stable output (1.07 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ngumoha offers stable output (1.07 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -41150,7 +41150,7 @@
       </c>
       <c r="Z452" t="inlineStr">
         <is>
-          <t>Chiesa offers stable output (0.58 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Chiesa offers stable output (0.58 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -41240,7 +41240,7 @@
       </c>
       <c r="Z453" t="inlineStr">
         <is>
-          <t>Gravenberch offers stable output (0.92 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gravenberch offers stable output (0.92 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -41330,7 +41330,7 @@
       </c>
       <c r="Z454" t="inlineStr">
         <is>
-          <t>Mac Allister offers stable output (2.77 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mac Allister offers stable output (2.77 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -41358,7 +41358,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G455" t="n">
@@ -41420,7 +41420,7 @@
       </c>
       <c r="Z455" t="inlineStr">
         <is>
-          <t>C.Jones offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>C.Jones carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Internazionale permanently; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="Z456" t="inlineStr">
         <is>
-          <t>Endo offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Endo offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -41600,7 +41600,7 @@
       </c>
       <c r="Z457" t="inlineStr">
         <is>
-          <t>Nyoni offers stable output (0.75 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Nyoni offers stable output (0.75 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -41628,7 +41628,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G458" t="n">
@@ -41690,7 +41690,7 @@
       </c>
       <c r="Z458" t="inlineStr">
         <is>
-          <t>Bajcetic offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bajcetic carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Celta Vigo permanently; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -41718,7 +41718,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G459" t="n">
@@ -41780,7 +41780,7 @@
       </c>
       <c r="Z459" t="inlineStr">
         <is>
-          <t>Munoz carries elevated risk for GW7 (2.09 exp pts). Concerns: Rotation risk (only 43% projected start); Tough offensive matchup (FDR: 1.3)</t>
+          <t>Munoz carries elevated risk for GW8 (2.09 exp pts). Concerns: Injury doubt: Knee injury - 75% chance of playing; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -41870,7 +41870,7 @@
       </c>
       <c r="Z460" t="inlineStr">
         <is>
-          <t>McConnell offers stable output (0.40 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>McConnell offers stable output (0.40 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -41960,7 +41960,7 @@
       </c>
       <c r="Z461" t="inlineStr">
         <is>
-          <t>Isak is projected for 4.48 pts in GW7 and 20.3 pts over next 5 weeks. Key drivers: Elite bookmaker goal probability (43.9% anytime); High-frequency chance generator (0.71 xG per 90)</t>
+          <t>Isak is projected for 4.48 pts in GW8 and 20.3 pts over next 5 weeks. Key drivers: Elite bookmaker goal probability (43.9% anytime); High-frequency chance generator (0.71 xG per 90)</t>
         </is>
       </c>
     </row>
@@ -41988,7 +41988,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G462" t="n">
@@ -42050,7 +42050,7 @@
       </c>
       <c r="Z462" t="inlineStr">
         <is>
-          <t>Ekitiké carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.3)</t>
+          <t>Ekitiké carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Achilles injury - Unknown return date; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -42140,7 +42140,7 @@
       </c>
       <c r="Z463" t="inlineStr">
         <is>
-          <t>Koumas offers stable output (1.20 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Koumas offers stable output (1.20 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -42230,7 +42230,7 @@
       </c>
       <c r="Z464" t="inlineStr">
         <is>
-          <t>Danns offers stable output (0.63 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Danns offers stable output (0.63 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -42258,7 +42258,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G465" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="Z465" t="inlineStr">
         <is>
-          <t>Elliott offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Elliott carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Valencia on loan for the rest of the season; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -42410,7 +42410,7 @@
       </c>
       <c r="Z466" t="inlineStr">
         <is>
-          <t>Araujo offers stable output (1.87 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Araujo offers stable output (1.87 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -42500,7 +42500,7 @@
       </c>
       <c r="Z467" t="inlineStr">
         <is>
-          <t>Barcola carries elevated risk for GW7 (2.43 exp pts). Concerns: Rotation risk (only 46% projected start); Tough offensive matchup (FDR: 1.3)</t>
+          <t>Barcola carries elevated risk for GW8 (2.43 exp pts). Concerns: Rotation risk (only 46% projected start); Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -42590,7 +42590,7 @@
       </c>
       <c r="Z468" t="inlineStr">
         <is>
-          <t>Enzo carries elevated risk for GW7 (2.04 exp pts). Concerns: Rotation risk (only 52% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Enzo carries elevated risk for GW8 (2.04 exp pts). Concerns: Rotation risk (only 52% projected start); Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -42680,7 +42680,7 @@
       </c>
       <c r="Z469" t="inlineStr">
         <is>
-          <t>Ndiaye offers stable output (3.72 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ndiaye offers stable output (3.72 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -42770,7 +42770,7 @@
       </c>
       <c r="Z470" t="inlineStr">
         <is>
-          <t>Donnarumma offers stable output (3.83 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Donnarumma offers stable output (3.83 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -42860,7 +42860,7 @@
       </c>
       <c r="Z471" t="inlineStr">
         <is>
-          <t>Bettinelli offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bettinelli offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -42888,7 +42888,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G472" t="n">
@@ -42950,7 +42950,7 @@
       </c>
       <c r="Z472" t="inlineStr">
         <is>
-          <t>O'Reilly carries elevated risk for GW7 (1.05 exp pts). Concerns: Rotation risk (only 17% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>O'Reilly carries elevated risk for GW8 (1.05 exp pts). Concerns: Injury doubt: Back injury - 75% chance of playing; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -43040,7 +43040,7 @@
       </c>
       <c r="Z473" t="inlineStr">
         <is>
-          <t>Guéhi carries elevated risk for GW7 (3.75 exp pts). Concerns: Regression warning: projected PPG is -1.62 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Guéhi carries elevated risk for GW8 (3.75 exp pts). Concerns: Regression warning: projected PPG is -1.62 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -43068,7 +43068,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G474" t="n">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="Z474" t="inlineStr">
         <is>
-          <t>Matheus N. offers stable output (1.51 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Matheus N. carries elevated risk for GW8 (1.51 exp pts). Concerns: Injury doubt: Unspecified injury - 75% chance of playing; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -43220,7 +43220,7 @@
       </c>
       <c r="Z475" t="inlineStr">
         <is>
-          <t>Rúben offers stable output (3.38 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Rúben offers stable output (3.38 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -43310,7 +43310,7 @@
       </c>
       <c r="Z476" t="inlineStr">
         <is>
-          <t>Gvardiol carries elevated risk for GW7 (2.96 exp pts). Concerns: Rotation risk (only 65% projected start); Regression warning: projected PPG is -3.16 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Gvardiol carries elevated risk for GW8 (2.96 exp pts). Concerns: Rotation risk (only 65% projected start); Regression warning: projected PPG is -3.16 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -43400,7 +43400,7 @@
       </c>
       <c r="Z477" t="inlineStr">
         <is>
-          <t>Aït-Nouri offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Aït-Nouri offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -43490,7 +43490,7 @@
       </c>
       <c r="Z478" t="inlineStr">
         <is>
-          <t>Khusanov offers stable output (0.87 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Khusanov offers stable output (0.87 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -43518,7 +43518,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G479" t="n">
@@ -43580,7 +43580,7 @@
       </c>
       <c r="Z479" t="inlineStr">
         <is>
-          <t>Alleyne offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Alleyne carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Burnley on loan for the rest of the season; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -43670,7 +43670,7 @@
       </c>
       <c r="Z480" t="inlineStr">
         <is>
-          <t>Lewis offers stable output (0.30 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lewis offers stable output (0.30 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -43760,7 +43760,7 @@
       </c>
       <c r="Z481" t="inlineStr">
         <is>
-          <t>Vitor Reis offers stable output (0.25 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Vitor Reis offers stable output (0.25 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -43788,7 +43788,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G482" t="n">
@@ -43850,7 +43850,7 @@
       </c>
       <c r="Z482" t="inlineStr">
         <is>
-          <t>Semenyo carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -3.15 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Semenyo carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Regression warning: projected PPG is -3.15 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -43940,7 +43940,7 @@
       </c>
       <c r="Z483" t="inlineStr">
         <is>
-          <t>Foden carries elevated risk for GW7 (1.73 exp pts). Concerns: Rotation risk (only 23% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Foden carries elevated risk for GW8 (1.73 exp pts). Concerns: Rotation risk (only 23% projected start); Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -44030,7 +44030,7 @@
       </c>
       <c r="Z484" t="inlineStr">
         <is>
-          <t>Cherki carries elevated risk for GW7 (3.38 exp pts). Concerns: Rotation risk (only 52% projected start); Regression warning: projected PPG is -4.31 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Cherki carries elevated risk for GW8 (3.38 exp pts). Concerns: Rotation risk (only 52% projected start); Regression warning: projected PPG is -4.31 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -44120,7 +44120,7 @@
       </c>
       <c r="Z485" t="inlineStr">
         <is>
-          <t>Doku carries elevated risk for GW7 (1.14 exp pts). Concerns: Rotation risk (only 9% projected start); Regression warning: projected PPG is -5.63 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Doku carries elevated risk for GW8 (1.14 exp pts). Concerns: Rotation risk (only 9% projected start); Regression warning: projected PPG is -5.63 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -44148,7 +44148,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G486" t="n">
@@ -44210,7 +44210,7 @@
       </c>
       <c r="Z486" t="inlineStr">
         <is>
-          <t>Rodrigo carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Rodrigo carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Barcelona permanently; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -44238,7 +44238,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G487" t="n">
@@ -44300,7 +44300,7 @@
       </c>
       <c r="Z487" t="inlineStr">
         <is>
-          <t>Reijnders carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Reijnders carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Al Qadsiah permanently; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -44328,7 +44328,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G488" t="n">
@@ -44390,7 +44390,7 @@
       </c>
       <c r="Z488" t="inlineStr">
         <is>
-          <t>Kovačić offers stable output (0.23 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kovačić carries elevated risk for GW8 (0.23 exp pts). Concerns: Injury doubt: Unspecified injury - 75% chance of playing; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -44418,7 +44418,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G489" t="n">
@@ -44480,7 +44480,7 @@
       </c>
       <c r="Z489" t="inlineStr">
         <is>
-          <t>Echeverri offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Echeverri carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Benfica on loan for the rest of the season; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -44508,7 +44508,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G490" t="n">
@@ -44570,7 +44570,7 @@
       </c>
       <c r="Z490" t="inlineStr">
         <is>
-          <t>Phillips offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Phillips carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Sheffield United on loan for the rest of the season; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -44598,7 +44598,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G491" t="n">
@@ -44660,7 +44660,7 @@
       </c>
       <c r="Z491" t="inlineStr">
         <is>
-          <t>Mukasa offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mukasa carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: has joined West Ham on loan for the rest of the seaon.; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -44688,7 +44688,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G492" t="n">
@@ -44750,7 +44750,7 @@
       </c>
       <c r="Z492" t="inlineStr">
         <is>
-          <t>Monga offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Monga carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Swansea City on loan for the rest of the season; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -44840,7 +44840,7 @@
       </c>
       <c r="Z493" t="inlineStr">
         <is>
-          <t>Haaland is projected for 5.59 pts in GW7 and 27.8 pts over next 5 weeks. Key drivers: Nailed starter (98% expected start probability); Elite bookmaker goal probability (57.9% anytime); High-frequency chance generator (0.83 xG per 90)</t>
+          <t>Haaland is projected for 5.59 pts in GW8 and 27.8 pts over next 5 weeks. Key drivers: Nailed starter (98% expected start probability); Elite bookmaker goal probability (57.9% anytime); High-frequency chance generator (0.83 xG per 90)</t>
         </is>
       </c>
     </row>
@@ -44930,7 +44930,7 @@
       </c>
       <c r="Z494" t="inlineStr">
         <is>
-          <t>Anderson offers stable output (2.76 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Anderson offers stable output (2.76 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -45020,7 +45020,7 @@
       </c>
       <c r="Z495" t="inlineStr">
         <is>
-          <t>Rulli offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Rulli offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -45110,7 +45110,7 @@
       </c>
       <c r="Z496" t="inlineStr">
         <is>
-          <t>Bouaddi offers stable output (0.50 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bouaddi offers stable output (0.50 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -45200,7 +45200,7 @@
       </c>
       <c r="Z497" t="inlineStr">
         <is>
-          <t>McAidoo offers stable output (0.70 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>McAidoo offers stable output (0.70 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -45290,7 +45290,7 @@
       </c>
       <c r="Z498" t="inlineStr">
         <is>
-          <t>Braithwaite offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Braithwaite offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -45380,7 +45380,7 @@
       </c>
       <c r="Z499" t="inlineStr">
         <is>
-          <t>Allan carries elevated risk for GW7 (0.67 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Allan carries elevated risk for GW8 (0.67 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -45470,7 +45470,7 @@
       </c>
       <c r="Z500" t="inlineStr">
         <is>
-          <t>Samba offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Samba offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -45560,7 +45560,7 @@
       </c>
       <c r="Z501" t="inlineStr">
         <is>
-          <t>Tielemans offers stable output (3.65 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tielemans offers stable output (3.65 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -45650,7 +45650,7 @@
       </c>
       <c r="Z502" t="inlineStr">
         <is>
-          <t>Baleba offers stable output (0.31 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Baleba offers stable output (0.31 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -45740,7 +45740,7 @@
       </c>
       <c r="Z503" t="inlineStr">
         <is>
-          <t>Andrey Santos offers stable output (0.74 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Andrey Santos offers stable output (0.74 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -45830,7 +45830,7 @@
       </c>
       <c r="Z504" t="inlineStr">
         <is>
-          <t>Darlow offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Darlow offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -45920,7 +45920,7 @@
       </c>
       <c r="Z505" t="inlineStr">
         <is>
-          <t>Lammens offers stable output (3.63 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lammens offers stable output (3.63 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -45948,7 +45948,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G506" t="n">
@@ -46010,7 +46010,7 @@
       </c>
       <c r="Z506" t="inlineStr">
         <is>
-          <t>Bayindir offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bayindir carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Celta Vigo on loan for the rest of the season; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -46100,7 +46100,7 @@
       </c>
       <c r="Z507" t="inlineStr">
         <is>
-          <t>Heaton offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Heaton offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -46128,7 +46128,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G508" t="n">
@@ -46190,7 +46190,7 @@
       </c>
       <c r="Z508" t="inlineStr">
         <is>
-          <t>Dorgu offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dorgu carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Expected back 25 Oct; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -46280,7 +46280,7 @@
       </c>
       <c r="Z509" t="inlineStr">
         <is>
-          <t>De Ligt offers stable output (0.24 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>De Ligt offers stable output (0.24 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -46370,7 +46370,7 @@
       </c>
       <c r="Z510" t="inlineStr">
         <is>
-          <t>Dalot offers stable output (2.09 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dalot offers stable output (2.09 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -46460,7 +46460,7 @@
       </c>
       <c r="Z511" t="inlineStr">
         <is>
-          <t>Maguire offers stable output (2.87 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Maguire offers stable output (2.87 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -46488,7 +46488,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G512" t="n">
@@ -46550,7 +46550,7 @@
       </c>
       <c r="Z512" t="inlineStr">
         <is>
-          <t>Martinez offers stable output (1.62 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Martinez carries elevated risk for GW8 (1.62 exp pts). Concerns: Injury doubt: Thigh injury - 75% chance of playing; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -46640,7 +46640,7 @@
       </c>
       <c r="Z513" t="inlineStr">
         <is>
-          <t>Yoro offers stable output (0.65 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Yoro offers stable output (0.65 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -46668,7 +46668,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G514" t="n">
@@ -46730,7 +46730,7 @@
       </c>
       <c r="Z514" t="inlineStr">
         <is>
-          <t>Heaven offers stable output (0.40 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Heaven carries elevated risk for GW8 (0.40 exp pts). Concerns: Injury doubt: Illness - 75% chance of playing; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -46820,7 +46820,7 @@
       </c>
       <c r="Z515" t="inlineStr">
         <is>
-          <t>Mazraoui offers stable output (0.58 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mazraoui offers stable output (0.58 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -46848,7 +46848,7 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G516" t="n">
@@ -46910,7 +46910,7 @@
       </c>
       <c r="Z516" t="inlineStr">
         <is>
-          <t>Shaw offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Shaw carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Unspecified injury - Unknown return date; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -47000,7 +47000,7 @@
       </c>
       <c r="Z517" t="inlineStr">
         <is>
-          <t>Amass offers stable output (0.23 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Amass offers stable output (0.23 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -47028,7 +47028,7 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G518" t="n">
@@ -47090,7 +47090,7 @@
       </c>
       <c r="Z518" t="inlineStr">
         <is>
-          <t>Fredricson offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Fredricson carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Lausanne-Sport permanently; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -47180,7 +47180,7 @@
       </c>
       <c r="Z519" t="inlineStr">
         <is>
-          <t>B.Fernandes offers stable output (3.90 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>B.Fernandes offers stable output (3.90 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -47270,7 +47270,7 @@
       </c>
       <c r="Z520" t="inlineStr">
         <is>
-          <t>Mbeumo is projected for 5.08 pts in GW7 and 24.3 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); Strong goal threat (39.5% anytime goal odds); High-frequency chance generator (0.57 xG per 90)</t>
+          <t>Mbeumo is projected for 5.08 pts in GW8 and 24.3 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); Strong goal threat (39.5% anytime goal odds); High-frequency chance generator (0.57 xG per 90)</t>
         </is>
       </c>
     </row>
@@ -47360,7 +47360,7 @@
       </c>
       <c r="Z521" t="inlineStr">
         <is>
-          <t>Cunha offers stable output (3.99 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Cunha offers stable output (3.99 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -47388,7 +47388,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G522" t="n">
@@ -47450,7 +47450,7 @@
       </c>
       <c r="Z522" t="inlineStr">
         <is>
-          <t>Rashford carries elevated risk for GW7 (2.25 exp pts). Concerns: Rotation risk (only 35% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Rashford carries elevated risk for GW8 (2.25 exp pts). Concerns: Injury doubt: Hip injury - 75% chance of playing; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -47540,7 +47540,7 @@
       </c>
       <c r="Z523" t="inlineStr">
         <is>
-          <t>Mount offers stable output (0.53 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mount offers stable output (0.53 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -47630,7 +47630,7 @@
       </c>
       <c r="Z524" t="inlineStr">
         <is>
-          <t>Amad offers stable output (1.16 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Amad offers stable output (1.16 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -47658,7 +47658,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G525" t="n">
@@ -47720,7 +47720,7 @@
       </c>
       <c r="Z525" t="inlineStr">
         <is>
-          <t>Mainoo carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -2.77 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Mainoo carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Unspecified injury - Expected back 8 Nov; Regression warning: projected PPG is -2.77 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -47748,7 +47748,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G526" t="n">
@@ -47810,7 +47810,7 @@
       </c>
       <c r="Z526" t="inlineStr">
         <is>
-          <t>Ugarte offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ugarte carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -47900,7 +47900,7 @@
       </c>
       <c r="Z527" t="inlineStr">
         <is>
-          <t>J.Fletcher offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>J.Fletcher offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -47990,7 +47990,7 @@
       </c>
       <c r="Z528" t="inlineStr">
         <is>
-          <t>Lacey offers stable output (0.73 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Lacey offers stable output (0.73 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -48018,7 +48018,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G529" t="n">
@@ -48080,7 +48080,7 @@
       </c>
       <c r="Z529" t="inlineStr">
         <is>
-          <t>Collyer offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Collyer carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined West Brom permanently; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -48170,7 +48170,7 @@
       </c>
       <c r="Z530" t="inlineStr">
         <is>
-          <t>Bendito Mantato offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bendito Mantato offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -48260,7 +48260,7 @@
       </c>
       <c r="Z531" t="inlineStr">
         <is>
-          <t>Fletcher offers stable output (0.40 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Fletcher offers stable output (0.40 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -48288,7 +48288,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G532" t="n">
@@ -48350,7 +48350,7 @@
       </c>
       <c r="Z532" t="inlineStr">
         <is>
-          <t>Šeško carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 1.2)</t>
+          <t>Šeško carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Shin injury - Unknown return date; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -48440,7 +48440,7 @@
       </c>
       <c r="Z533" t="inlineStr">
         <is>
-          <t>Zirkzee offers stable output (0.65 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Zirkzee offers stable output (0.65 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -48468,7 +48468,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G534" t="n">
@@ -48530,7 +48530,7 @@
       </c>
       <c r="Z534" t="inlineStr">
         <is>
-          <t>Obi offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Obi carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Willem II on loan for the rest of the season; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -48620,7 +48620,7 @@
       </c>
       <c r="Z535" t="inlineStr">
         <is>
-          <t>N.Gonzalez offers stable output (1.59 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>N.Gonzalez offers stable output (1.59 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -48710,7 +48710,7 @@
       </c>
       <c r="Z536" t="inlineStr">
         <is>
-          <t>Pope offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Pope offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -48800,7 +48800,7 @@
       </c>
       <c r="Z537" t="inlineStr">
         <is>
-          <t>Gillespie offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gillespie offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -48828,7 +48828,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G538" t="n">
@@ -48890,7 +48890,7 @@
       </c>
       <c r="Z538" t="inlineStr">
         <is>
-          <t>Jaouen offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Jaouen carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Unknown return date; Low defensive odds; clean sheet unlikely (24.9%); Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -48980,7 +48980,7 @@
       </c>
       <c r="Z539" t="inlineStr">
         <is>
-          <t>Thiaw offers stable output (2.59 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Thiaw offers stable output (2.59 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -49070,7 +49070,7 @@
       </c>
       <c r="Z540" t="inlineStr">
         <is>
-          <t>Schär offers stable output (0.01 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Schär offers stable output (0.01 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -49160,7 +49160,7 @@
       </c>
       <c r="Z541" t="inlineStr">
         <is>
-          <t>Botman offers stable output (2.50 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Botman offers stable output (2.50 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -49250,7 +49250,7 @@
       </c>
       <c r="Z542" t="inlineStr">
         <is>
-          <t>Burn offers stable output (0.23 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Burn offers stable output (0.23 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -49340,7 +49340,7 @@
       </c>
       <c r="Z543" t="inlineStr">
         <is>
-          <t>Hall carries elevated risk for GW7 (3.49 exp pts). Concerns: Low defensive odds; clean sheet unlikely (24.9%); Regression warning: projected PPG is -1.41 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
+          <t>Hall carries elevated risk for GW8 (3.49 exp pts). Concerns: Low defensive odds; clean sheet unlikely (24.9%); Regression warning: projected PPG is -1.41 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G544" t="n">
@@ -49430,7 +49430,7 @@
       </c>
       <c r="Z544" t="inlineStr">
         <is>
-          <t>Livramento offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Livramento carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Expected back 7 Nov; Low defensive odds; clean sheet unlikely (24.9%); Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -49458,7 +49458,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G545" t="n">
@@ -49520,7 +49520,7 @@
       </c>
       <c r="Z545" t="inlineStr">
         <is>
-          <t>A.Murphy offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>A.Murphy carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined FC Kaiserslautern on loan for the rest of the season; Low defensive odds; clean sheet unlikely (24.9%); Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -49610,7 +49610,7 @@
       </c>
       <c r="Z546" t="inlineStr">
         <is>
-          <t>Barnes offers stable output (4.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Barnes offers stable output (4.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -49638,7 +49638,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G547" t="n">
@@ -49700,7 +49700,7 @@
       </c>
       <c r="Z547" t="inlineStr">
         <is>
-          <t>Elanga carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -5.55 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
+          <t>Elanga carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Unspecified injury - Expected back 25 Oct; Regression warning: projected PPG is -5.55 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -49728,7 +49728,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G548" t="n">
@@ -49790,7 +49790,7 @@
       </c>
       <c r="Z548" t="inlineStr">
         <is>
-          <t>J.Ramsey offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>J.Ramsey carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Thigh injury - Unknown return date; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -49880,7 +49880,7 @@
       </c>
       <c r="Z549" t="inlineStr">
         <is>
-          <t>J.Murphy offers stable output (1.05 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>J.Murphy offers stable output (1.05 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -49970,7 +49970,7 @@
       </c>
       <c r="Z550" t="inlineStr">
         <is>
-          <t>Joelinton offers stable output (0.17 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Joelinton offers stable output (0.17 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -50060,7 +50060,7 @@
       </c>
       <c r="Z551" t="inlineStr">
         <is>
-          <t>L.Miley offers stable output (2.68 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>L.Miley offers stable output (2.68 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -50150,7 +50150,7 @@
       </c>
       <c r="Z552" t="inlineStr">
         <is>
-          <t>Willock offers stable output (2.69 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Willock offers stable output (2.69 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -50240,7 +50240,7 @@
       </c>
       <c r="Z553" t="inlineStr">
         <is>
-          <t>Touré offers stable output (0.34 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Touré offers stable output (0.34 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -50330,7 +50330,7 @@
       </c>
       <c r="Z554" t="inlineStr">
         <is>
-          <t>Steur offers stable output (0.88 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Steur offers stable output (0.88 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -50358,7 +50358,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G555" t="n">
@@ -50420,7 +50420,7 @@
       </c>
       <c r="Z555" t="inlineStr">
         <is>
-          <t>Woltemade carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -3.99 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
+          <t>Woltemade carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Juventus on loan for the rest of the season; Regression warning: projected PPG is -3.99 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -50510,7 +50510,7 @@
       </c>
       <c r="Z556" t="inlineStr">
         <is>
-          <t>Wissa offers stable output (3.18 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Wissa offers stable output (3.18 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -50600,7 +50600,7 @@
       </c>
       <c r="Z557" t="inlineStr">
         <is>
-          <t>Osula offers stable output (1.03 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Osula offers stable output (1.03 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -50628,7 +50628,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G558" t="n">
@@ -50690,7 +50690,7 @@
       </c>
       <c r="Z558" t="inlineStr">
         <is>
-          <t>Neave offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Neave carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Wolves on loan for the rest of the season; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -50780,7 +50780,7 @@
       </c>
       <c r="Z559" t="inlineStr">
         <is>
-          <t>Bamba offers stable output (0.31 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bamba offers stable output (0.31 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -50870,7 +50870,7 @@
       </c>
       <c r="Z560" t="inlineStr">
         <is>
-          <t>Horníček offers stable output (3.28 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Horníček offers stable output (3.28 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -50960,7 +50960,7 @@
       </c>
       <c r="Z561" t="inlineStr">
         <is>
-          <t>Dedić offers stable output (1.90 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dedić offers stable output (1.90 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G562" t="n">
@@ -51050,7 +51050,7 @@
       </c>
       <c r="Z562" t="inlineStr">
         <is>
-          <t>Shahar offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Shahar carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: has joined Arouca on loan for the rest of the seaon.; Low defensive odds; clean sheet unlikely (24.9%); Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -51140,7 +51140,7 @@
       </c>
       <c r="Z563" t="inlineStr">
         <is>
-          <t>Fernandez-Pardo carries elevated risk for GW7 (1.49 exp pts). Concerns: Rotation risk (only 23% projected start); Tough offensive matchup (FDR: 1.0)</t>
+          <t>Fernandez-Pardo carries elevated risk for GW8 (1.49 exp pts). Concerns: Rotation risk (only 23% projected start); Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -51230,7 +51230,7 @@
       </c>
       <c r="Z564" t="inlineStr">
         <is>
-          <t>Miley offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Miley offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -51320,7 +51320,7 @@
       </c>
       <c r="Z565" t="inlineStr">
         <is>
-          <t>Pivas offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Pivas offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -51410,7 +51410,7 @@
       </c>
       <c r="Z566" t="inlineStr">
         <is>
-          <t>Salia offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Salia offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -51500,7 +51500,7 @@
       </c>
       <c r="Z567" t="inlineStr">
         <is>
-          <t>Mills offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mills offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -51590,7 +51590,7 @@
       </c>
       <c r="Z568" t="inlineStr">
         <is>
-          <t>Thompson offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Thompson offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -51680,7 +51680,7 @@
       </c>
       <c r="Z569" t="inlineStr">
         <is>
-          <t>Delap offers stable output (2.86 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Delap offers stable output (2.86 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -51770,7 +51770,7 @@
       </c>
       <c r="Z570" t="inlineStr">
         <is>
-          <t>Muñoz offers stable output (2.48 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Muñoz offers stable output (2.48 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -51860,7 +51860,7 @@
       </c>
       <c r="Z571" t="inlineStr">
         <is>
-          <t>Sels offers stable output (3.47 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Sels offers stable output (3.47 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -51950,7 +51950,7 @@
       </c>
       <c r="Z572" t="inlineStr">
         <is>
-          <t>John offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>John offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -52040,7 +52040,7 @@
       </c>
       <c r="Z573" t="inlineStr">
         <is>
-          <t>N.Williams offers stable output (3.34 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>N.Williams offers stable output (3.34 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -52068,7 +52068,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G574" t="n">
@@ -52130,7 +52130,7 @@
       </c>
       <c r="Z574" t="inlineStr">
         <is>
-          <t>Morato offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Morato carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined West Ham on loan for the rest of the season; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -52220,7 +52220,7 @@
       </c>
       <c r="Z575" t="inlineStr">
         <is>
-          <t>Milenković carries elevated risk for GW7 (0.64 exp pts). Concerns: Rotation risk (only 21% projected start); Regression warning: projected PPG is -3.36 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Milenković carries elevated risk for GW8 (0.64 exp pts). Concerns: Rotation risk (only 21% projected start); Regression warning: projected PPG is -3.36 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -52310,7 +52310,7 @@
       </c>
       <c r="Z576" t="inlineStr">
         <is>
-          <t>Murillo offers stable output (3.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Murillo offers stable output (3.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -52400,7 +52400,7 @@
       </c>
       <c r="Z577" t="inlineStr">
         <is>
-          <t>Aina offers stable output (1.66 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Aina offers stable output (1.66 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -52490,7 +52490,7 @@
       </c>
       <c r="Z578" t="inlineStr">
         <is>
-          <t>Jair Cunha offers stable output (2.03 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Jair Cunha offers stable output (2.03 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -52518,7 +52518,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G579" t="n">
@@ -52580,7 +52580,7 @@
       </c>
       <c r="Z579" t="inlineStr">
         <is>
-          <t>Savona offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Savona carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -52670,7 +52670,7 @@
       </c>
       <c r="Z580" t="inlineStr">
         <is>
-          <t>O.Richards offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>O.Richards offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -52698,7 +52698,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G581" t="n">
@@ -52760,7 +52760,7 @@
       </c>
       <c r="Z581" t="inlineStr">
         <is>
-          <t>Abbott offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Abbott carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Southampton on loan for the rest of the season; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -52850,7 +52850,7 @@
       </c>
       <c r="Z582" t="inlineStr">
         <is>
-          <t>Netz offers stable output (0.26 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Netz offers stable output (0.26 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -52878,7 +52878,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G583" t="n">
@@ -52940,7 +52940,7 @@
       </c>
       <c r="Z583" t="inlineStr">
         <is>
-          <t>Bindon offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bindon carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Charlton Athletic on loan for the rest of the season; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -53030,7 +53030,7 @@
       </c>
       <c r="Z584" t="inlineStr">
         <is>
-          <t>Gibbs-White is projected for 4.55 pts in GW7 and 20.4 pts over next 5 weeks. Key drivers: Strong goal threat (36.1% anytime goal odds); Primary creative playmaker (0.31 xA per 90); Designated penalty taker</t>
+          <t>Gibbs-White is projected for 4.55 pts in GW8 and 20.4 pts over next 5 weeks. Key drivers: Strong goal threat (36.1% anytime goal odds); Primary creative playmaker (0.31 xA per 90); Designated penalty taker</t>
         </is>
       </c>
     </row>
@@ -53120,7 +53120,7 @@
       </c>
       <c r="Z585" t="inlineStr">
         <is>
-          <t>Hudson-Odoi offers stable output (0.67 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hudson-Odoi offers stable output (0.67 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -53210,7 +53210,7 @@
       </c>
       <c r="Z586" t="inlineStr">
         <is>
-          <t>Ndoye offers stable output (3.34 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ndoye offers stable output (3.34 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -53238,7 +53238,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G587" t="n">
@@ -53300,7 +53300,7 @@
       </c>
       <c r="Z587" t="inlineStr">
         <is>
-          <t>Hutchinson offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hutchinson carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined AC Milan on loan for the rest of the season; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -53328,7 +53328,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G588" t="n">
@@ -53390,7 +53390,7 @@
       </c>
       <c r="Z588" t="inlineStr">
         <is>
-          <t>Bakwa offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bakwa carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Lille on loan for the rest of the season; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -53480,7 +53480,7 @@
       </c>
       <c r="Z589" t="inlineStr">
         <is>
-          <t>McAtee offers stable output (3.12 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>McAtee offers stable output (3.12 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -53570,7 +53570,7 @@
       </c>
       <c r="Z590" t="inlineStr">
         <is>
-          <t>Dominguez offers stable output (0.22 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dominguez offers stable output (0.22 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -53660,7 +53660,7 @@
       </c>
       <c r="Z591" t="inlineStr">
         <is>
-          <t>I.Sangaré offers stable output (0.43 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>I.Sangaré offers stable output (0.43 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -53750,7 +53750,7 @@
       </c>
       <c r="Z592" t="inlineStr">
         <is>
-          <t>Yates offers stable output (0.33 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Yates offers stable output (0.33 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -53840,7 +53840,7 @@
       </c>
       <c r="Z593" t="inlineStr">
         <is>
-          <t>Wood offers stable output (0.97 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Wood offers stable output (0.97 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -53868,7 +53868,7 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -53930,7 +53930,7 @@
       </c>
       <c r="Z594" t="inlineStr">
         <is>
-          <t>Igor Jesus offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Igor Jesus carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Calf injury - Unknown return date; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -54020,7 +54020,7 @@
       </c>
       <c r="Z595" t="inlineStr">
         <is>
-          <t>Kalimuendo offers stable output (0.69 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kalimuendo offers stable output (0.69 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -54110,7 +54110,7 @@
       </c>
       <c r="Z596" t="inlineStr">
         <is>
-          <t>Schlager offers stable output (2.77 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Schlager offers stable output (2.77 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -54200,7 +54200,7 @@
       </c>
       <c r="Z597" t="inlineStr">
         <is>
-          <t>Diomande offers stable output (1.74 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Diomande offers stable output (1.74 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -54290,7 +54290,7 @@
       </c>
       <c r="Z598" t="inlineStr">
         <is>
-          <t>Benda offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Benda offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -54380,7 +54380,7 @@
       </c>
       <c r="Z599" t="inlineStr">
         <is>
-          <t>Van Hecke carries elevated risk for GW7 (2.21 exp pts). Concerns: Low defensive odds; clean sheet unlikely (17.0%); Regression warning: projected PPG is -1.46 lower than past form; Tough offensive matchup (FDR: 0.8)</t>
+          <t>Van Hecke carries elevated risk for GW8 (2.21 exp pts). Concerns: Low defensive odds; clean sheet unlikely (17.0%); Regression warning: projected PPG is -1.46 lower than past form; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -54408,7 +54408,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G600" t="n">
@@ -54470,7 +54470,7 @@
       </c>
       <c r="Z600" t="inlineStr">
         <is>
-          <t>Tosin offers stable output (0.32 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tosin carries elevated risk for GW8 (0.32 exp pts). Concerns: Injury doubt: Calf injury - 75% chance of playing; Low defensive odds; clean sheet unlikely (17.0%); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -54498,7 +54498,7 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G601" t="n">
@@ -54560,7 +54560,7 @@
       </c>
       <c r="Z601" t="inlineStr">
         <is>
-          <t>Marmoush carries elevated risk for GW7 (2.36 exp pts). Concerns: Rotation risk (only 45% projected start); Tough offensive matchup (FDR: 0.8)</t>
+          <t>Marmoush carries elevated risk for GW8 (2.36 exp pts). Concerns: Injury doubt: Calf injury - 75% chance of playing; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -54588,7 +54588,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G602" t="n">
@@ -54650,7 +54650,7 @@
       </c>
       <c r="Z602" t="inlineStr">
         <is>
-          <t>Sávio carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 0.8)</t>
+          <t>Sávio carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Muscular injury - Expected back 7 Nov; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -54740,7 +54740,7 @@
       </c>
       <c r="Z603" t="inlineStr">
         <is>
-          <t>Tonali offers stable output (3.12 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tonali offers stable output (3.12 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -54768,7 +54768,7 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G604" t="n">
@@ -54830,7 +54830,7 @@
       </c>
       <c r="Z604" t="inlineStr">
         <is>
-          <t>Vicario offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Vicario carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Juventus on loan for the rest of the season; Low defensive odds; clean sheet unlikely (17.0%); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -54920,7 +54920,7 @@
       </c>
       <c r="Z605" t="inlineStr">
         <is>
-          <t>Austin offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Austin offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -55010,7 +55010,7 @@
       </c>
       <c r="Z606" t="inlineStr">
         <is>
-          <t>Kinsky offers stable output (2.53 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Kinsky offers stable output (2.53 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -55100,7 +55100,7 @@
       </c>
       <c r="Z607" t="inlineStr">
         <is>
-          <t>Dubravka offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Dubravka offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -55190,7 +55190,7 @@
       </c>
       <c r="Z608" t="inlineStr">
         <is>
-          <t>Senesi offers stable output (0.45 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Senesi offers stable output (0.45 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -55218,7 +55218,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G609" t="n">
@@ -55280,7 +55280,7 @@
       </c>
       <c r="Z609" t="inlineStr">
         <is>
-          <t>Pedro Porro offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Pedro Porro carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Expected back 24 Oct; Low defensive odds; clean sheet unlikely (17.0%); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -55308,7 +55308,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G610" t="n">
@@ -55370,7 +55370,7 @@
       </c>
       <c r="Z610" t="inlineStr">
         <is>
-          <t>Romero offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Romero carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Atletico Madrid permanently; Low defensive odds; clean sheet unlikely (17.0%); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -55398,7 +55398,7 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G611" t="n">
@@ -55460,7 +55460,7 @@
       </c>
       <c r="Z611" t="inlineStr">
         <is>
-          <t>Robertson offers stable output (1.72 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Robertson carries elevated risk for GW8 (1.72 exp pts). Concerns: Injury doubt: Foot injury - 75% chance of playing; Low defensive odds; clean sheet unlikely (17.0%); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -55550,7 +55550,7 @@
       </c>
       <c r="Z612" t="inlineStr">
         <is>
-          <t>Van de Ven offers stable output (2.30 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Van de Ven offers stable output (2.30 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -55578,7 +55578,7 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G613" t="n">
@@ -55640,7 +55640,7 @@
       </c>
       <c r="Z613" t="inlineStr">
         <is>
-          <t>Spence offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Spence carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Internazionale permanently; Low defensive odds; clean sheet unlikely (17.0%); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -55668,7 +55668,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G614" t="n">
@@ -55730,7 +55730,7 @@
       </c>
       <c r="Z614" t="inlineStr">
         <is>
-          <t>Udogie offers stable output (0.41 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Udogie carries elevated risk for GW8 (0.41 exp pts). Concerns: Injury doubt: Knee injury - 75% chance of playing; Low defensive odds; clean sheet unlikely (17.0%); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -55758,7 +55758,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G615" t="n">
@@ -55820,7 +55820,7 @@
       </c>
       <c r="Z615" t="inlineStr">
         <is>
-          <t>Phillips offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Phillips carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Middlesbrough permanently; Low defensive odds; clean sheet unlikely (17.0%); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -55910,7 +55910,7 @@
       </c>
       <c r="Z616" t="inlineStr">
         <is>
-          <t>Davies carries elevated risk for GW7 (0.21 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (17.0%); Regression warning: projected PPG is -6.95 lower than past form</t>
+          <t>Davies carries elevated risk for GW8 (0.21 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (17.0%); Regression warning: projected PPG is -6.95 lower than past form</t>
         </is>
       </c>
     </row>
@@ -56000,7 +56000,7 @@
       </c>
       <c r="Z617" t="inlineStr">
         <is>
-          <t>Byfield offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Byfield offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -56090,7 +56090,7 @@
       </c>
       <c r="Z618" t="inlineStr">
         <is>
-          <t>Rowswell offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Rowswell offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -56118,7 +56118,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G619" t="n">
@@ -56180,7 +56180,7 @@
       </c>
       <c r="Z619" t="inlineStr">
         <is>
-          <t>Souza offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Souza carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined FC Porto on loan for the rest of the season; Low defensive odds; clean sheet unlikely (17.0%); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -56270,7 +56270,7 @@
       </c>
       <c r="Z620" t="inlineStr">
         <is>
-          <t>Kudus carries elevated risk for GW7 (1.30 exp pts). Concerns: Rotation risk (only 21% projected start); Tough offensive matchup (FDR: 0.8)</t>
+          <t>Kudus carries elevated risk for GW8 (1.30 exp pts). Concerns: Rotation risk (only 21% projected start); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -56298,7 +56298,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G621" t="n">
@@ -56360,7 +56360,7 @@
       </c>
       <c r="Z621" t="inlineStr">
         <is>
-          <t>Xavi offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Xavi carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -56450,7 +56450,7 @@
       </c>
       <c r="Z622" t="inlineStr">
         <is>
-          <t>Tel offers stable output (1.26 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tel offers stable output (1.26 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -56540,7 +56540,7 @@
       </c>
       <c r="Z623" t="inlineStr">
         <is>
-          <t>Maddison carries elevated risk for GW7 (0.97 exp pts). Concerns: Rotation risk (only 11% projected start); Tough offensive matchup (FDR: 0.8)</t>
+          <t>Maddison carries elevated risk for GW8 (0.97 exp pts). Concerns: Rotation risk (only 11% projected start); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -56568,7 +56568,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G624" t="n">
@@ -56630,7 +56630,7 @@
       </c>
       <c r="Z624" t="inlineStr">
         <is>
-          <t>Bentancur offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bentancur carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Suspended until 7 Nov; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -56658,7 +56658,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G625" t="n">
@@ -56720,7 +56720,7 @@
       </c>
       <c r="Z625" t="inlineStr">
         <is>
-          <t>Odobert offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Odobert carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -56748,7 +56748,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G626" t="n">
@@ -56810,7 +56810,7 @@
       </c>
       <c r="Z626" t="inlineStr">
         <is>
-          <t>P.M.Sarr offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>P.M.Sarr carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Juventus on loan for the rest of the season; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -56900,7 +56900,7 @@
       </c>
       <c r="Z627" t="inlineStr">
         <is>
-          <t>Gallagher offers stable output (0.93 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gallagher offers stable output (0.93 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -56928,7 +56928,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G628" t="n">
@@ -56990,7 +56990,7 @@
       </c>
       <c r="Z628" t="inlineStr">
         <is>
-          <t>Bergvall offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Bergvall carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Expected back 31 Oct; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -57080,7 +57080,7 @@
       </c>
       <c r="Z629" t="inlineStr">
         <is>
-          <t>Kulusevski carries elevated risk for GW7 (0.50 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 0.8)</t>
+          <t>Kulusevski carries elevated risk for GW8 (0.50 exp pts). Concerns: Rotation risk (only 0% projected start); Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -57170,7 +57170,7 @@
       </c>
       <c r="Z630" t="inlineStr">
         <is>
-          <t>Gray offers stable output (2.38 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Gray offers stable output (2.38 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -57198,7 +57198,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G631" t="n">
@@ -57260,7 +57260,7 @@
       </c>
       <c r="Z631" t="inlineStr">
         <is>
-          <t>Moore offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Moore carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined FC Köln on loan for the rest of the season; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -57350,7 +57350,7 @@
       </c>
       <c r="Z632" t="inlineStr">
         <is>
-          <t>Olusesi offers stable output (0.32 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Olusesi offers stable output (0.32 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -57440,7 +57440,7 @@
       </c>
       <c r="Z633" t="inlineStr">
         <is>
-          <t>Fernandes offers stable output (1.02 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Fernandes offers stable output (1.02 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -57530,7 +57530,7 @@
       </c>
       <c r="Z634" t="inlineStr">
         <is>
-          <t>Solanke offers stable output (1.97 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Solanke offers stable output (1.97 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -57558,7 +57558,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G635" t="n">
@@ -57620,7 +57620,7 @@
       </c>
       <c r="Z635" t="inlineStr">
         <is>
-          <t>Richarlison offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Richarlison carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: not included in squad.; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -57648,7 +57648,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G636" t="n">
@@ -57710,7 +57710,7 @@
       </c>
       <c r="Z636" t="inlineStr">
         <is>
-          <t>Scarlett offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Scarlett carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Leyton Orient permanently; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -57738,7 +57738,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G637" t="n">
@@ -57800,7 +57800,7 @@
       </c>
       <c r="Z637" t="inlineStr">
         <is>
-          <t>Mudryk offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mudryk carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Ankle injury - Unknown return date; Tough offensive matchup (FDR: 0.8)</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="Z638" t="inlineStr">
         <is>
-          <t>Williams-Barnett offers stable output (0.48 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Williams-Barnett offers stable output (0.48 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -57918,7 +57918,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G639" t="n">
@@ -57980,7 +57980,7 @@
       </c>
       <c r="Z639" t="inlineStr">
         <is>
-          <t>Danso offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Danso carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Suspended until 31 Oct; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -58070,7 +58070,7 @@
       </c>
       <c r="Z640" t="inlineStr">
         <is>
-          <t>Roefs offers stable output (3.44 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Roefs offers stable output (3.44 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -58098,7 +58098,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G641" t="n">
@@ -58160,7 +58160,7 @@
       </c>
       <c r="Z641" t="inlineStr">
         <is>
-          <t>Patterson offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Patterson carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Wrexham permanently; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -58250,7 +58250,7 @@
       </c>
       <c r="Z642" t="inlineStr">
         <is>
-          <t>Ellborg offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ellborg offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -58278,7 +58278,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G643" t="n">
@@ -58340,7 +58340,7 @@
       </c>
       <c r="Z643" t="inlineStr">
         <is>
-          <t>Ballard offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ballard carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Unknown return date; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -58430,7 +58430,7 @@
       </c>
       <c r="Z644" t="inlineStr">
         <is>
-          <t>Mukiele offers stable output (3.20 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mukiele offers stable output (3.20 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -58520,7 +58520,7 @@
       </c>
       <c r="Z645" t="inlineStr">
         <is>
-          <t>Hume offers stable output (2.20 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hume offers stable output (2.20 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -58610,7 +58610,7 @@
       </c>
       <c r="Z646" t="inlineStr">
         <is>
-          <t>Alderete offers stable output (0.39 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Alderete offers stable output (0.39 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -58700,7 +58700,7 @@
       </c>
       <c r="Z647" t="inlineStr">
         <is>
-          <t>Reinildo offers stable output (2.28 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Reinildo offers stable output (2.28 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -58728,7 +58728,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G648" t="n">
@@ -58790,7 +58790,7 @@
       </c>
       <c r="Z648" t="inlineStr">
         <is>
-          <t>Seelt offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Seelt carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Swansea City on loan for the rest of the season; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -58818,7 +58818,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G649" t="n">
@@ -58880,7 +58880,7 @@
       </c>
       <c r="Z649" t="inlineStr">
         <is>
-          <t>Hjelde offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Hjelde carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined KV Mechelen on loan for the rest of the season; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -58970,7 +58970,7 @@
       </c>
       <c r="Z650" t="inlineStr">
         <is>
-          <t>O'Nien offers stable output (0.35 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>O'Nien offers stable output (0.35 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -58998,7 +58998,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G651" t="n">
@@ -59060,7 +59060,7 @@
       </c>
       <c r="Z651" t="inlineStr">
         <is>
-          <t>Masuaku offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Masuaku carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Konyaspor permanently; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -59088,7 +59088,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G652" t="n">
@@ -59150,7 +59150,7 @@
       </c>
       <c r="Z652" t="inlineStr">
         <is>
-          <t>Meunier offers stable output (1.72 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Meunier carries elevated risk for GW8 (1.72 exp pts). Concerns: Injury doubt: Groin injury - 75% chance of playing; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -59240,7 +59240,7 @@
       </c>
       <c r="Z653" t="inlineStr">
         <is>
-          <t>E.Le Fée offers stable output (4.04 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>E.Le Fée offers stable output (4.04 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -59330,7 +59330,7 @@
       </c>
       <c r="Z654" t="inlineStr">
         <is>
-          <t>Diarra offers stable output (0.43 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Diarra offers stable output (0.43 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -59420,7 +59420,7 @@
       </c>
       <c r="Z655" t="inlineStr">
         <is>
-          <t>Xhaka offers stable output (3.36 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Xhaka offers stable output (3.36 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -59510,7 +59510,7 @@
       </c>
       <c r="Z656" t="inlineStr">
         <is>
-          <t>Sadiki offers stable output (2.91 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Sadiki offers stable output (2.91 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -59538,7 +59538,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G657" t="n">
@@ -59600,7 +59600,7 @@
       </c>
       <c r="Z657" t="inlineStr">
         <is>
-          <t>Adingra offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Adingra carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Ajax on loan for the rest of the season; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -59628,7 +59628,7 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G658" t="n">
@@ -59690,7 +59690,7 @@
       </c>
       <c r="Z658" t="inlineStr">
         <is>
-          <t>Mundle offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Mundle carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -59780,7 +59780,7 @@
       </c>
       <c r="Z659" t="inlineStr">
         <is>
-          <t>Rigg offers stable output (0.61 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Rigg offers stable output (0.61 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -59870,7 +59870,7 @@
       </c>
       <c r="Z660" t="inlineStr">
         <is>
-          <t>Talbi offers stable output (0.53 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Talbi offers stable output (0.53 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -59960,7 +59960,7 @@
       </c>
       <c r="Z661" t="inlineStr">
         <is>
-          <t>Jocelin.T offers stable output (0.42 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Jocelin.T offers stable output (0.42 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -60050,7 +60050,7 @@
       </c>
       <c r="Z662" t="inlineStr">
         <is>
-          <t>N.Angulo offers stable output (1.92 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>N.Angulo offers stable output (1.92 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -60078,7 +60078,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G663" t="n">
@@ -60140,7 +60140,7 @@
       </c>
       <c r="Z663" t="inlineStr">
         <is>
-          <t>Brobbey carries elevated risk for GW7 (2.55 exp pts). Concerns: Rotation risk (only 40% projected start); Regression warning: projected PPG is -2.18 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Brobbey carries elevated risk for GW8 (2.55 exp pts). Concerns: Injury doubt: Hamstring injury - 75% chance of playing; Regression warning: projected PPG is -2.18 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -60168,7 +60168,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G664" t="n">
@@ -60230,7 +60230,7 @@
       </c>
       <c r="Z664" t="inlineStr">
         <is>
-          <t>Isidor offers stable output (1.12 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Isidor carries elevated risk for GW8 (1.12 exp pts). Concerns: Injury doubt: Knock - 50% chance of playing; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -60320,7 +60320,7 @@
       </c>
       <c r="Z665" t="inlineStr">
         <is>
-          <t>Methalie offers stable output (0.19 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Methalie offers stable output (0.19 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -60410,7 +60410,7 @@
       </c>
       <c r="Z666" t="inlineStr">
         <is>
-          <t>Ahoka offers stable output (0.28 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Ahoka offers stable output (0.28 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -60500,7 +60500,7 @@
       </c>
       <c r="Z667" t="inlineStr">
         <is>
-          <t>Fofana offers stable output (0.35 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Fofana offers stable output (0.35 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -60590,7 +60590,7 @@
       </c>
       <c r="Z668" t="inlineStr">
         <is>
-          <t>J.Angulo offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>J.Angulo offers stable output (0.00 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -60680,7 +60680,7 @@
       </c>
       <c r="Z669" t="inlineStr">
         <is>
-          <t>Tutierov offers stable output (0.03 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Tutierov offers stable output (0.03 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -60695,7 +60695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60844,7 +60844,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Haaland is projected for 5.59 pts in GW7 and 27.8 pts over next 5 weeks. Key drivers: Nailed starter (98% expected start probability); Elite bookmaker goal probability (57.9% anytime); High-frequency chance generator (0.83 xG per 90)</t>
+          <t>Haaland is projected for 5.59 pts in GW8 and 27.8 pts over next 5 weeks. Key drivers: Nailed starter (98% expected start probability); Elite bookmaker goal probability (57.9% anytime); High-frequency chance generator (0.83 xG per 90)</t>
         </is>
       </c>
     </row>
@@ -60907,7 +60907,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Mbeumo is projected for 5.08 pts in GW7 and 24.3 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); Strong goal threat (39.5% anytime goal odds); High-frequency chance generator (0.57 xG per 90)</t>
+          <t>Mbeumo is projected for 5.08 pts in GW8 and 24.3 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); Strong goal threat (39.5% anytime goal odds); High-frequency chance generator (0.57 xG per 90)</t>
         </is>
       </c>
     </row>
@@ -60970,31 +60970,31 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Tavernier is projected for 4.45 pts in GW7 and 23.4 pts over next 5 weeks. Key drivers: Nailed starter (91% expected start probability); Strong goal threat (29.7% anytime goal odds); High-frequency chance generator (0.45 xG per 90)</t>
+          <t>Tavernier is projected for 4.45 pts in GW8 and 23.4 pts over next 5 weeks. Key drivers: Nailed starter (91% expected start probability); Strong goal threat (29.7% anytime goal odds); High-frequency chance generator (0.45 xG per 90)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>385</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saka</t>
+          <t>Trafford</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -61002,53 +61002,53 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>4.13</v>
       </c>
       <c r="I5" t="n">
-        <v>4.87</v>
+        <v>4.37</v>
       </c>
       <c r="J5" t="n">
-        <v>4.75</v>
+        <v>3.97</v>
       </c>
       <c r="K5" t="n">
-        <v>4.29</v>
+        <v>4.51</v>
       </c>
       <c r="L5" t="n">
-        <v>22.16</v>
+        <v>21.48</v>
       </c>
       <c r="M5" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8679999999999994</v>
+        <v>-0.3040000000000003</v>
       </c>
       <c r="O5" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Saka is projected for 3.95 pts in GW7 and 22.2 pts over next 5 weeks. Key drivers: Strong goal threat (36.5% anytime goal odds); High-frequency chance generator (0.55 xG per 90); Designated penalty taker</t>
+          <t>Trafford is projected for 4.50 pts in GW8 and 21.5 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); Strong save volume floor (3.7 saves/90)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>385</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Trafford</t>
+          <t>Raya</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -61057,36 +61057,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Strong Buy</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4.5</v>
+        <v>5.08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.13</v>
+        <v>3.91</v>
       </c>
       <c r="I6" t="n">
-        <v>4.37</v>
+        <v>4.34</v>
       </c>
       <c r="J6" t="n">
-        <v>3.97</v>
+        <v>4.15</v>
       </c>
       <c r="K6" t="n">
-        <v>4.51</v>
+        <v>3.87</v>
       </c>
       <c r="L6" t="n">
-        <v>21.48</v>
+        <v>21.35</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3040000000000003</v>
+        <v>-1.73</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -61096,80 +61096,80 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Trafford is projected for 4.50 pts in GW7 and 21.5 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); Strong save volume floor (3.7 saves/90)</t>
+          <t>Raya is projected for 5.08 pts in GW8 and 21.4 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); High clean sheet odds for upcoming fixture (47.3%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Raya</t>
+          <t>De Cuyper</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strong Buy</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5.08</v>
+        <v>3.74</v>
       </c>
       <c r="H7" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
       <c r="I7" t="n">
-        <v>4.34</v>
+        <v>4.44</v>
       </c>
       <c r="J7" t="n">
-        <v>4.15</v>
+        <v>4.44</v>
       </c>
       <c r="K7" t="n">
-        <v>3.87</v>
+        <v>4.49</v>
       </c>
       <c r="L7" t="n">
-        <v>21.35</v>
+        <v>21.19</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.73</v>
+        <v>-4.161999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Raya is projected for 5.08 pts in GW7 and 21.4 pts over next 5 weeks. Key drivers: Nailed starter (100% expected start probability); High clean sheet odds for upcoming fixture (47.3%)</t>
+          <t>De Cuyper is projected for 3.74 pts in GW8 and 21.2 pts over next 5 weeks. Key drivers: Nailed starter (92% expected start probability); Attacking defender upside (0.28 xG/90, 0.12 xA/90)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>De Cuyper</t>
+          <t>Groß</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -61179,11 +61179,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -61191,62 +61191,62 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3.74</v>
+        <v>4.02</v>
       </c>
       <c r="H8" t="n">
-        <v>4.08</v>
+        <v>3.99</v>
       </c>
       <c r="I8" t="n">
-        <v>4.44</v>
+        <v>4.36</v>
       </c>
       <c r="J8" t="n">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="K8" t="n">
-        <v>4.49</v>
+        <v>4.35</v>
       </c>
       <c r="L8" t="n">
-        <v>21.19</v>
+        <v>21.1</v>
       </c>
       <c r="M8" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.161999999999999</v>
+        <v>-4.08</v>
       </c>
       <c r="O8" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="P8" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>De Cuyper is projected for 3.74 pts in GW7 and 21.2 pts over next 5 weeks. Key drivers: Nailed starter (92% expected start probability); Attacking defender upside (0.28 xG/90, 0.12 xA/90)</t>
+          <t>Groß is projected for 4.02 pts in GW8 and 21.1 pts over next 5 weeks. Key drivers: Nailed starter (96% expected start probability); Designated penalty taker</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Groß</t>
+          <t>Calafiori</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -61254,48 +61254,48 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4.02</v>
+        <v>4.92</v>
       </c>
       <c r="H9" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="J9" t="n">
         <v>3.99</v>
       </c>
-      <c r="I9" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.38</v>
-      </c>
       <c r="K9" t="n">
-        <v>4.35</v>
+        <v>3.74</v>
       </c>
       <c r="L9" t="n">
-        <v>21.1</v>
+        <v>20.57</v>
       </c>
       <c r="M9" t="n">
-        <v>8.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.08</v>
+        <v>-2.186</v>
       </c>
       <c r="O9" t="n">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="P9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Groß is projected for 4.02 pts in GW7 and 21.1 pts over next 5 weeks. Key drivers: Nailed starter (96% expected start probability); Designated penalty taker</t>
+          <t>Calafiori is projected for 4.92 pts in GW8 and 20.6 pts over next 5 weeks. Key drivers: Nailed starter (93% expected start probability); High clean sheet odds for upcoming fixture (47.3%); Attacking defender upside (0.19 xG/90, 0.15 xA/90)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Calafiori</t>
+          <t>Ødegaard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -61305,11 +61305,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -61317,53 +61317,53 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4.92</v>
+        <v>4.36</v>
       </c>
       <c r="H10" t="n">
-        <v>3.77</v>
+        <v>3.89</v>
       </c>
       <c r="I10" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="J10" t="n">
         <v>4.15</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.99</v>
-      </c>
       <c r="K10" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>20.57</v>
+        <v>20.44</v>
       </c>
       <c r="M10" t="n">
-        <v>6.3</v>
+        <v>4.7</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.186</v>
+        <v>-0.6120000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.19</v>
+        <v>0.31</v>
       </c>
       <c r="P10" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Calafiori is projected for 4.92 pts in GW7 and 20.6 pts over next 5 weeks. Key drivers: Nailed starter (93% expected start probability); High clean sheet odds for upcoming fixture (47.3%); Attacking defender upside (0.19 xG/90, 0.15 xA/90)</t>
+          <t>Ødegaard is projected for 4.36 pts in GW8 and 20.4 pts over next 5 weeks. Key drivers: Primary creative playmaker (0.26 xA per 90)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15</v>
+        <v>480</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ødegaard</t>
+          <t>Gibbs-White</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Nott'm Forest</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -61372,7 +61372,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -61380,62 +61380,62 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4.36</v>
+        <v>4.55</v>
       </c>
       <c r="H11" t="n">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
       <c r="I11" t="n">
-        <v>4.24</v>
+        <v>3.81</v>
       </c>
       <c r="J11" t="n">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>4.06</v>
       </c>
       <c r="L11" t="n">
-        <v>20.44</v>
+        <v>20.39</v>
       </c>
       <c r="M11" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6120000000000001</v>
+        <v>-0.9220000000000006</v>
       </c>
       <c r="O11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P11" t="n">
         <v>0.31</v>
       </c>
-      <c r="P11" t="n">
-        <v>0.26</v>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Ødegaard is projected for 4.36 pts in GW7 and 20.4 pts over next 5 weeks. Key drivers: Primary creative playmaker (0.26 xA per 90)</t>
+          <t>Gibbs-White is projected for 4.55 pts in GW8 and 20.4 pts over next 5 weeks. Key drivers: Strong goal threat (36.1% anytime goal odds); Primary creative playmaker (0.31 xA per 90); Designated penalty taker</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>480</v>
+        <v>379</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gibbs-White</t>
+          <t>Isak</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nott'm Forest</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -61443,62 +61443,62 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="H12" t="n">
-        <v>3.98</v>
+        <v>3.78</v>
       </c>
       <c r="I12" t="n">
-        <v>3.81</v>
+        <v>4.05</v>
       </c>
       <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.99</v>
       </c>
-      <c r="K12" t="n">
-        <v>4.06</v>
-      </c>
       <c r="L12" t="n">
-        <v>20.39</v>
+        <v>20.3</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9220000000000006</v>
+        <v>-2.94</v>
       </c>
       <c r="O12" t="n">
-        <v>0.28</v>
+        <v>0.71</v>
       </c>
       <c r="P12" t="n">
-        <v>0.31</v>
+        <v>0.02</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Gibbs-White is projected for 4.55 pts in GW7 and 20.4 pts over next 5 weeks. Key drivers: Strong goal threat (36.1% anytime goal odds); Primary creative playmaker (0.31 xA per 90); Designated penalty taker</t>
+          <t>Isak is projected for 4.48 pts in GW8 and 20.3 pts over next 5 weeks. Key drivers: Elite bookmaker goal probability (43.9% anytime); High-frequency chance generator (0.71 xG per 90)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>379</v>
+        <v>261</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Isak</t>
+          <t>Iwobi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -61506,53 +61506,53 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4.48</v>
+        <v>4.27</v>
       </c>
       <c r="H13" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.05</v>
       </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.99</v>
-      </c>
       <c r="L13" t="n">
-        <v>20.3</v>
+        <v>19.89</v>
       </c>
       <c r="M13" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.94</v>
+        <v>-0.1219999999999994</v>
       </c>
       <c r="O13" t="n">
-        <v>0.71</v>
+        <v>0.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0.02</v>
+        <v>0.36</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Isak is projected for 4.48 pts in GW7 and 20.3 pts over next 5 weeks. Key drivers: Elite bookmaker goal probability (43.9% anytime); High-frequency chance generator (0.71 xG per 90)</t>
+          <t>Iwobi is projected for 4.27 pts in GW8 and 19.9 pts over next 5 weeks. Key drivers: Nailed starter (92% expected start probability); Primary creative playmaker (0.36 xA per 90)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>261</v>
+        <v>94</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Iwobi</t>
+          <t>Schade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -61561,7 +61561,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -61569,53 +61569,53 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4.27</v>
+        <v>4.36</v>
       </c>
       <c r="H14" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>19.89</v>
+        <v>19.7</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1219999999999994</v>
+        <v>-1.76</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="P14" t="n">
-        <v>0.36</v>
+        <v>0.06</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Iwobi is projected for 4.27 pts in GW7 and 19.9 pts over next 5 weeks. Key drivers: Nailed starter (92% expected start probability); Primary creative playmaker (0.36 xA per 90)</t>
+          <t>Schade is projected for 4.36 pts in GW8 and 19.7 pts over next 5 weeks. Key drivers: Strong goal threat (35.5% anytime goal odds)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Schade</t>
+          <t>Rogers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -61624,7 +61624,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -61632,48 +61632,48 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="H15" t="n">
-        <v>3.89</v>
+        <v>3.79</v>
       </c>
       <c r="I15" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="L15" t="n">
-        <v>19.7</v>
+        <v>19.62</v>
       </c>
       <c r="M15" t="n">
         <v>5.7</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.76</v>
+        <v>-1.776000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="P15" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Schade is projected for 4.36 pts in GW7 and 19.7 pts over next 5 weeks. Key drivers: Strong goal threat (35.5% anytime goal odds)</t>
+          <t>Rogers is projected for 4.34 pts in GW8 and 19.6 pts over next 5 weeks. Key drivers: Nailed starter (96% expected start probability); Strong goal threat (36.0% anytime goal odds)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rogers</t>
+          <t>Palmer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -61687,7 +61687,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -61695,101 +61695,38 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4.34</v>
+        <v>4.22</v>
       </c>
       <c r="H16" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="I16" t="n">
-        <v>3.84</v>
+        <v>3.48</v>
       </c>
       <c r="J16" t="n">
-        <v>3.93</v>
+        <v>3.54</v>
       </c>
       <c r="K16" t="n">
-        <v>3.72</v>
+        <v>3.38</v>
       </c>
       <c r="L16" t="n">
-        <v>19.62</v>
+        <v>18.06</v>
       </c>
       <c r="M16" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.776000000000001</v>
+        <v>-1.788000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Rogers is projected for 4.34 pts in GW7 and 19.6 pts over next 5 weeks. Key drivers: Nailed starter (96% expected start probability); Strong goal threat (36.0% anytime goal odds)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>154</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Palmer</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="L17" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="M17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-1.788000000000001</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Palmer is projected for 4.22 pts in GW7 and 18.1 pts over next 5 weeks. Key drivers: Nailed starter (98% expected start probability); Elite bookmaker goal probability (41.5% anytime); Designated penalty taker</t>
+          <t>Palmer is projected for 4.22 pts in GW8 and 18.1 pts over next 5 weeks. Key drivers: Nailed starter (98% expected start probability); Elite bookmaker goal probability (41.5% anytime); Designated penalty taker</t>
         </is>
       </c>
     </row>
@@ -61953,7 +61890,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Hinshelwood carries elevated risk for GW7 (0.89 exp pts). Concerns: Rotation risk (only 6% projected start); Regression warning: projected PPG is -10.49 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Hinshelwood carries elevated risk for GW8 (0.89 exp pts). Concerns: Rotation risk (only 6% projected start); Regression warning: projected PPG is -10.49 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -62016,7 +61953,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Davies carries elevated risk for GW7 (0.21 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (17.0%); Regression warning: projected PPG is -6.95 lower than past form</t>
+          <t>Davies carries elevated risk for GW8 (0.21 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (17.0%); Regression warning: projected PPG is -6.95 lower than past form</t>
         </is>
       </c>
     </row>
@@ -62079,7 +62016,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Henderson carries elevated risk for GW7 (1.21 exp pts). Concerns: Rotation risk (only 21% projected start); Regression warning: projected PPG is -6.71 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
+          <t>Henderson carries elevated risk for GW8 (1.21 exp pts). Concerns: Rotation risk (only 21% projected start); Regression warning: projected PPG is -6.71 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -62107,7 +62044,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -62142,7 +62079,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Manzambi carries elevated risk for GW7 (1.42 exp pts). Concerns: Rotation risk (only 15% projected start); Regression warning: projected PPG is -6.32 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Manzambi carries elevated risk for GW8 (1.42 exp pts). Concerns: Injury doubt: Calf injury - 75% chance of playing; Regression warning: projected PPG is -6.32 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -62205,7 +62142,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Mfuni carries elevated risk for GW7 (0.52 exp pts). Concerns: Rotation risk (only 7% projected start); Low defensive odds; clean sheet unlikely (23.9%); Regression warning: projected PPG is -6.18 lower than past form</t>
+          <t>Mfuni carries elevated risk for GW8 (0.52 exp pts). Concerns: Rotation risk (only 7% projected start); Low defensive odds; clean sheet unlikely (23.9%); Regression warning: projected PPG is -6.18 lower than past form</t>
         </is>
       </c>
     </row>
@@ -62268,7 +62205,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Carvalho carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -6.00 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Carvalho carries elevated risk for GW8 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -6.00 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -62331,7 +62268,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Doku carries elevated risk for GW7 (1.14 exp pts). Concerns: Rotation risk (only 9% projected start); Regression warning: projected PPG is -5.63 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Doku carries elevated risk for GW8 (1.14 exp pts). Concerns: Rotation risk (only 9% projected start); Regression warning: projected PPG is -5.63 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -62359,7 +62296,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -62394,7 +62331,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Elanga carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -5.55 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
+          <t>Elanga carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Unspecified injury - Expected back 25 Oct; Regression warning: projected PPG is -5.55 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -62457,7 +62394,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Mosquera carries elevated risk for GW7 (0.68 exp pts). Concerns: Rotation risk (only 13% projected start); Regression warning: projected PPG is -5.52 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Mosquera carries elevated risk for GW8 (0.68 exp pts). Concerns: Rotation risk (only 13% projected start); Regression warning: projected PPG is -5.52 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -62485,7 +62422,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -62520,7 +62457,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Schuster carries elevated risk for GW7 (0.96 exp pts). Concerns: Rotation risk (only 17% projected start); Regression warning: projected PPG is -4.62 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Schuster carries elevated risk for GW8 (0.96 exp pts). Concerns: Injury doubt: Ankle injury - 75% chance of playing; Regression warning: projected PPG is -4.62 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -62548,7 +62485,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -62583,7 +62520,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Mendy carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (19.3%); Regression warning: projected PPG is -4.52 lower than past form</t>
+          <t>Mendy carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Groin injury - Expected back 31 Oct; Low defensive odds; clean sheet unlikely (19.3%); Regression warning: projected PPG is -4.52 lower than past form</t>
         </is>
       </c>
     </row>
@@ -62611,7 +62548,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -62646,7 +62583,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Scott carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -4.34 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Scott carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Thigh injury - Expected back 8 Nov; Regression warning: projected PPG is -4.34 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -62709,7 +62646,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Cherki carries elevated risk for GW7 (3.38 exp pts). Concerns: Rotation risk (only 52% projected start); Regression warning: projected PPG is -4.31 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Cherki carries elevated risk for GW8 (3.38 exp pts). Concerns: Rotation risk (only 52% projected start); Regression warning: projected PPG is -4.31 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -62772,7 +62709,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Maitland-Niles carries elevated risk for GW7 (1.06 exp pts). Concerns: Rotation risk (only 24% projected start); Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -4.25 lower than past form</t>
+          <t>Maitland-Niles carries elevated risk for GW8 (1.06 exp pts). Concerns: Rotation risk (only 24% projected start); Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -4.25 lower than past form</t>
         </is>
       </c>
     </row>
@@ -62835,7 +62772,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>De Cuyper is projected for 3.74 pts in GW7 and 21.2 pts over next 5 weeks. Key drivers: Nailed starter (92% expected start probability); Attacking defender upside (0.28 xG/90, 0.12 xA/90)</t>
+          <t>De Cuyper is projected for 3.74 pts in GW8 and 21.2 pts over next 5 weeks. Key drivers: Nailed starter (92% expected start probability); Attacking defender upside (0.28 xG/90, 0.12 xA/90)</t>
         </is>
       </c>
     </row>
@@ -62898,7 +62835,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Groß is projected for 4.02 pts in GW7 and 21.1 pts over next 5 weeks. Key drivers: Nailed starter (96% expected start probability); Designated penalty taker</t>
+          <t>Groß is projected for 4.02 pts in GW8 and 21.1 pts over next 5 weeks. Key drivers: Nailed starter (96% expected start probability); Designated penalty taker</t>
         </is>
       </c>
     </row>
@@ -62926,7 +62863,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -62961,7 +62898,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Woltemade carries elevated risk for GW7 (0.00 exp pts). Concerns: Rotation risk (only 0% projected start); Regression warning: projected PPG is -3.99 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
+          <t>Woltemade carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Has joined Juventus on loan for the rest of the season; Regression warning: projected PPG is -3.99 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -63024,7 +62961,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>João Pedro offers stable output (3.97 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>João Pedro offers stable output (3.97 exp pts in GW8) without standout fixtures or acute rotation danger.</t>
         </is>
       </c>
     </row>
@@ -63087,7 +63024,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Cherif carries elevated risk for GW7 (1.17 exp pts). Concerns: Rotation risk (only 13% projected start); Regression warning: projected PPG is -3.97 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
+          <t>Cherif carries elevated risk for GW8 (1.17 exp pts). Concerns: Rotation risk (only 13% projected start); Regression warning: projected PPG is -3.97 lower than past form; Tough offensive matchup (FDR: 1.0)</t>
         </is>
       </c>
     </row>
@@ -63150,7 +63087,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Hadjam carries elevated risk for GW7 (0.27 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -3.94 lower than past form</t>
+          <t>Hadjam carries elevated risk for GW8 (0.27 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -3.94 lower than past form</t>
         </is>
       </c>
     </row>
@@ -63213,7 +63150,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Chilwell carries elevated risk for GW7 (0.36 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (22.2%); Regression warning: projected PPG is -3.92 lower than past form</t>
+          <t>Chilwell carries elevated risk for GW8 (0.36 exp pts). Concerns: Rotation risk (only 0% projected start); Low defensive odds; clean sheet unlikely (22.2%); Regression warning: projected PPG is -3.92 lower than past form</t>
         </is>
       </c>
     </row>
@@ -63276,7 +63213,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Vuskovic carries elevated risk for GW7 (2.89 exp pts). Concerns: Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -3.86 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Vuskovic carries elevated risk for GW8 (2.89 exp pts). Concerns: Low defensive odds; clean sheet unlikely (20.5%); Regression warning: projected PPG is -3.86 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -63339,7 +63276,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Gakpo carries elevated risk for GW7 (3.15 exp pts). Concerns: Rotation risk (only 49% projected start); Regression warning: projected PPG is -3.86 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
+          <t>Gakpo carries elevated risk for GW8 (3.15 exp pts). Concerns: Rotation risk (only 49% projected start); Regression warning: projected PPG is -3.86 lower than past form; Tough offensive matchup (FDR: 1.3)</t>
         </is>
       </c>
     </row>
@@ -63402,7 +63339,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Affengruber carries elevated risk for GW7 (1.77 exp pts). Concerns: Rotation risk (only 48% projected start); Regression warning: projected PPG is -3.57 lower than past form; Tough offensive matchup (FDR: 1.5)</t>
+          <t>Affengruber carries elevated risk for GW8 (1.77 exp pts). Concerns: Rotation risk (only 48% projected start); Regression warning: projected PPG is -3.57 lower than past form; Tough offensive matchup (FDR: 1.5)</t>
         </is>
       </c>
     </row>
@@ -63465,7 +63402,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Bruno G. carries elevated risk for GW7 (0.77 exp pts). Concerns: Rotation risk (only 17% projected start); Regression warning: projected PPG is -3.45 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
+          <t>Bruno G. carries elevated risk for GW8 (0.77 exp pts). Concerns: Rotation risk (only 17% projected start); Regression warning: projected PPG is -3.45 lower than past form; Tough offensive matchup (FDR: 1.2)</t>
         </is>
       </c>
     </row>
@@ -63528,7 +63465,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Tarkowski carries elevated risk for GW7 (2.57 exp pts). Concerns: Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -3.44 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Tarkowski carries elevated risk for GW8 (2.57 exp pts). Concerns: Low defensive odds; clean sheet unlikely (18.2%); Regression warning: projected PPG is -3.44 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -63591,7 +63528,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Milenković carries elevated risk for GW7 (0.64 exp pts). Concerns: Rotation risk (only 21% projected start); Regression warning: projected PPG is -3.36 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
+          <t>Milenković carries elevated risk for GW8 (0.64 exp pts). Concerns: Rotation risk (only 21% projected start); Regression warning: projected PPG is -3.36 lower than past form; Tough offensive matchup (FDR: 1.4)</t>
         </is>
       </c>
     </row>
@@ -63654,7 +63591,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Andrés carries elevated risk for GW7 (1.02 exp pts). Concerns: Rotation risk (only 22% projected start); Regression warning: projected PPG is -3.35 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
+          <t>Andrés carries elevated risk for GW8 (1.02 exp pts). Concerns: Rotation risk (only 22% projected start); Regression warning: projected PPG is -3.35 lower than past form; Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
@@ -63682,7 +63619,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -63717,7 +63654,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Rodon offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Rodon carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Hamstring injury - Expected back 21 Nov; Tough offensive matchup (FDR: 1.1)</t>
         </is>
       </c>
     </row>
@@ -63745,7 +63682,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid (Injured)</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -63780,7 +63717,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Wieffer offers stable output (0.00 exp pts in GW7) without standout fixtures or acute rotation danger.</t>
+          <t>Wieffer carries elevated risk for GW8 (0.00 exp pts). Concerns: Injured / Out: Knee injury - Unknown return date; Low defensive odds; clean sheet unlikely (20.5%); Tough offensive matchup (FDR: 0.9)</t>
         </is>
       </c>
     </row>
